--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8599A9C1-59E8-4887-B75A-04A85309248A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003631C2-CA49-4C65-8485-504752E6D679}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="345">
   <si>
     <t>PRESUPUESTO TOTAL</t>
   </si>
@@ -1045,6 +1045,24 @@
   </si>
   <si>
     <t>Fatima</t>
+  </si>
+  <si>
+    <t>Centro</t>
+  </si>
+  <si>
+    <t>Izp</t>
+  </si>
+  <si>
+    <t>General</t>
+  </si>
+  <si>
+    <t>Hospital</t>
+  </si>
+  <si>
+    <t>Estadio</t>
+  </si>
+  <si>
+    <t>Graderia</t>
   </si>
 </sst>
 </file>
@@ -1495,13 +1513,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5391,7 +5409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FB8E136-486C-4EB9-920D-6287CDC3043B}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="32"/>
@@ -5474,16 +5492,345 @@
         <v>11419.96</v>
       </c>
       <c r="I2" s="72">
-        <f t="shared" ref="I2:J2" si="0">C2/$B$2</f>
+        <f>C2/B2</f>
         <v>0.49710716525496096</v>
       </c>
       <c r="J2" s="72">
-        <f t="shared" si="0"/>
+        <f>D2/B2</f>
         <v>0.75770847201117075</v>
       </c>
       <c r="K2" s="68">
         <f>B2-C2</f>
         <v>22037.563618134853</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="71" t="s">
+        <v>339</v>
+      </c>
+      <c r="B3" s="68">
+        <v>10000</v>
+      </c>
+      <c r="C3" s="69">
+        <v>2000</v>
+      </c>
+      <c r="D3" s="68">
+        <v>5000</v>
+      </c>
+      <c r="E3" s="68">
+        <v>21785.03</v>
+      </c>
+      <c r="F3" s="68">
+        <f t="shared" ref="F3:F10" si="0">C3-D3</f>
+        <v>-3000</v>
+      </c>
+      <c r="G3" s="68">
+        <f t="shared" ref="G3:G10" si="1">C3-E3</f>
+        <v>-19785.03</v>
+      </c>
+      <c r="H3" s="68">
+        <f t="shared" ref="H3:H10" si="2">D3-E3</f>
+        <v>-16785.03</v>
+      </c>
+      <c r="I3" s="72">
+        <f t="shared" ref="I3:I10" si="3">C3/B3</f>
+        <v>0.2</v>
+      </c>
+      <c r="J3" s="72">
+        <f t="shared" ref="J3:J10" si="4">D3/B3</f>
+        <v>0.5</v>
+      </c>
+      <c r="K3" s="68">
+        <f t="shared" ref="K3:K10" si="5">B3-C3</f>
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="71" t="s">
+        <v>340</v>
+      </c>
+      <c r="B4" s="68">
+        <v>50000</v>
+      </c>
+      <c r="C4" s="69">
+        <v>25000</v>
+      </c>
+      <c r="D4" s="68">
+        <v>28000</v>
+      </c>
+      <c r="E4" s="68">
+        <v>21786.03</v>
+      </c>
+      <c r="F4" s="68">
+        <f t="shared" si="0"/>
+        <v>-3000</v>
+      </c>
+      <c r="G4" s="68">
+        <f t="shared" si="1"/>
+        <v>3213.9700000000012</v>
+      </c>
+      <c r="H4" s="68">
+        <f t="shared" si="2"/>
+        <v>6213.9700000000012</v>
+      </c>
+      <c r="I4" s="72">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="J4" s="72">
+        <f t="shared" si="4"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="K4" s="68">
+        <f t="shared" si="5"/>
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="71" t="s">
+        <v>341</v>
+      </c>
+      <c r="B5" s="68">
+        <v>25000</v>
+      </c>
+      <c r="C5" s="69">
+        <f>Dashboard!C17</f>
+        <v>17239.126381865146</v>
+      </c>
+      <c r="D5" s="68">
+        <v>20000</v>
+      </c>
+      <c r="E5" s="68">
+        <v>21787.03</v>
+      </c>
+      <c r="F5" s="68">
+        <f t="shared" si="0"/>
+        <v>-2760.873618134854</v>
+      </c>
+      <c r="G5" s="68">
+        <f t="shared" si="1"/>
+        <v>-4547.9036181348529</v>
+      </c>
+      <c r="H5" s="68">
+        <f t="shared" si="2"/>
+        <v>-1787.0299999999988</v>
+      </c>
+      <c r="I5" s="72">
+        <f t="shared" si="3"/>
+        <v>0.68956505527460588</v>
+      </c>
+      <c r="J5" s="72">
+        <f t="shared" si="4"/>
+        <v>0.8</v>
+      </c>
+      <c r="K5" s="68">
+        <f t="shared" si="5"/>
+        <v>7760.873618134854</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="71" t="s">
+        <v>342</v>
+      </c>
+      <c r="B6" s="68">
+        <v>50000</v>
+      </c>
+      <c r="C6" s="69">
+        <v>23000</v>
+      </c>
+      <c r="D6" s="68">
+        <v>30000</v>
+      </c>
+      <c r="E6" s="68">
+        <v>21788.03</v>
+      </c>
+      <c r="F6" s="68">
+        <f t="shared" si="0"/>
+        <v>-7000</v>
+      </c>
+      <c r="G6" s="68">
+        <f t="shared" si="1"/>
+        <v>1211.9700000000012</v>
+      </c>
+      <c r="H6" s="68">
+        <f t="shared" si="2"/>
+        <v>8211.9700000000012</v>
+      </c>
+      <c r="I6" s="72">
+        <f t="shared" si="3"/>
+        <v>0.46</v>
+      </c>
+      <c r="J6" s="72">
+        <f t="shared" si="4"/>
+        <v>0.6</v>
+      </c>
+      <c r="K6" s="68">
+        <f t="shared" si="5"/>
+        <v>27000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="71" t="s">
+        <v>343</v>
+      </c>
+      <c r="B7" s="68">
+        <v>60000</v>
+      </c>
+      <c r="C7" s="69">
+        <v>12000</v>
+      </c>
+      <c r="D7" s="68">
+        <v>30000</v>
+      </c>
+      <c r="E7" s="68">
+        <v>21789.03</v>
+      </c>
+      <c r="F7" s="68">
+        <f t="shared" si="0"/>
+        <v>-18000</v>
+      </c>
+      <c r="G7" s="68">
+        <f t="shared" si="1"/>
+        <v>-9789.0299999999988</v>
+      </c>
+      <c r="H7" s="68">
+        <f t="shared" si="2"/>
+        <v>8210.9700000000012</v>
+      </c>
+      <c r="I7" s="72">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+      <c r="J7" s="72">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="K7" s="68">
+        <f t="shared" si="5"/>
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="71" t="s">
+        <v>344</v>
+      </c>
+      <c r="B8" s="68">
+        <v>70000</v>
+      </c>
+      <c r="C8" s="69">
+        <v>35000</v>
+      </c>
+      <c r="D8" s="68">
+        <v>35000</v>
+      </c>
+      <c r="E8" s="68">
+        <v>21790.03</v>
+      </c>
+      <c r="F8" s="68">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="68">
+        <f t="shared" si="1"/>
+        <v>13209.970000000001</v>
+      </c>
+      <c r="H8" s="68">
+        <f t="shared" si="2"/>
+        <v>13209.970000000001</v>
+      </c>
+      <c r="I8" s="72">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="J8" s="72">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="K8" s="68">
+        <f t="shared" si="5"/>
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="71" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="68">
+        <v>60000</v>
+      </c>
+      <c r="C9" s="69">
+        <v>25000</v>
+      </c>
+      <c r="D9" s="68">
+        <v>30000</v>
+      </c>
+      <c r="E9" s="68">
+        <v>21791.03</v>
+      </c>
+      <c r="F9" s="68">
+        <f t="shared" si="0"/>
+        <v>-5000</v>
+      </c>
+      <c r="G9" s="68">
+        <f t="shared" si="1"/>
+        <v>3208.9700000000012</v>
+      </c>
+      <c r="H9" s="68">
+        <f t="shared" si="2"/>
+        <v>8208.9700000000012</v>
+      </c>
+      <c r="I9" s="72">
+        <f t="shared" si="3"/>
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="J9" s="72">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="K9" s="68">
+        <f t="shared" si="5"/>
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="71" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" s="68">
+        <v>45000</v>
+      </c>
+      <c r="C10" s="69">
+        <v>20000</v>
+      </c>
+      <c r="D10" s="68">
+        <v>20000</v>
+      </c>
+      <c r="E10" s="68">
+        <v>21792.03</v>
+      </c>
+      <c r="F10" s="68">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="68">
+        <f t="shared" si="1"/>
+        <v>-1792.0299999999988</v>
+      </c>
+      <c r="H10" s="68">
+        <f t="shared" si="2"/>
+        <v>-1792.0299999999988</v>
+      </c>
+      <c r="I10" s="72">
+        <f t="shared" si="3"/>
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="J10" s="72">
+        <f t="shared" si="4"/>
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="K10" s="68">
+        <f t="shared" si="5"/>
+        <v>25000</v>
       </c>
     </row>
   </sheetData>
@@ -5507,28 +5854,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
@@ -5564,7 +5911,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="74"/>
-      <c r="G5" s="76">
+      <c r="G5" s="78">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5614,7 +5961,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="74"/>
-      <c r="G8" s="76">
+      <c r="G8" s="78">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -5848,6 +6195,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -5857,14 +6212,6 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5884,20 +6231,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6039,32 +6386,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10512,38 +10859,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003631C2-CA49-4C65-8485-504752E6D679}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C95BED-26CA-402F-88D5-C9A1696350FC}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1513,13 +1513,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5854,28 +5854,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
@@ -5911,7 +5911,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="74"/>
-      <c r="G5" s="78">
+      <c r="G5" s="76">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5961,7 +5961,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="74"/>
-      <c r="G8" s="78">
+      <c r="G8" s="76">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -6195,14 +6195,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6212,6 +6204,14 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6231,20 +6231,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6386,32 +6386,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10859,38 +10859,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86C95BED-26CA-402F-88D5-C9A1696350FC}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDE0FD2B-DE2F-4425-94EA-D67C6058382D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="345">
   <si>
     <t>PRESUPUESTO TOTAL</t>
   </si>
@@ -1513,13 +1513,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5752,86 +5752,28 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="71" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" s="68">
-        <v>60000</v>
-      </c>
-      <c r="C9" s="69">
-        <v>25000</v>
-      </c>
-      <c r="D9" s="68">
-        <v>30000</v>
-      </c>
-      <c r="E9" s="68">
-        <v>21791.03</v>
-      </c>
-      <c r="F9" s="68">
-        <f t="shared" si="0"/>
-        <v>-5000</v>
-      </c>
-      <c r="G9" s="68">
-        <f t="shared" si="1"/>
-        <v>3208.9700000000012</v>
-      </c>
-      <c r="H9" s="68">
-        <f t="shared" si="2"/>
-        <v>8208.9700000000012</v>
-      </c>
-      <c r="I9" s="72">
-        <f t="shared" si="3"/>
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="J9" s="72">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-      <c r="K9" s="68">
-        <f t="shared" si="5"/>
-        <v>35000</v>
-      </c>
+      <c r="A9" s="71"/>
+      <c r="B9" s="68"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="72"/>
+      <c r="K9" s="68"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="71" t="s">
-        <v>97</v>
-      </c>
-      <c r="B10" s="68">
-        <v>45000</v>
-      </c>
-      <c r="C10" s="69">
-        <v>20000</v>
-      </c>
-      <c r="D10" s="68">
-        <v>20000</v>
-      </c>
-      <c r="E10" s="68">
-        <v>21792.03</v>
-      </c>
-      <c r="F10" s="68">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G10" s="68">
-        <f t="shared" si="1"/>
-        <v>-1792.0299999999988</v>
-      </c>
-      <c r="H10" s="68">
-        <f t="shared" si="2"/>
-        <v>-1792.0299999999988</v>
-      </c>
-      <c r="I10" s="72">
-        <f t="shared" si="3"/>
-        <v>0.44444444444444442</v>
-      </c>
-      <c r="J10" s="72">
-        <f t="shared" si="4"/>
-        <v>0.44444444444444442</v>
-      </c>
-      <c r="K10" s="68">
-        <f t="shared" si="5"/>
-        <v>25000</v>
-      </c>
+      <c r="A10" s="71"/>
+      <c r="B10" s="68"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="72"/>
+      <c r="K10" s="68"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5854,28 +5796,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
@@ -5911,7 +5853,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="74"/>
-      <c r="G5" s="76">
+      <c r="G5" s="78">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5961,7 +5903,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="74"/>
-      <c r="G8" s="76">
+      <c r="G8" s="78">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -6195,6 +6137,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6204,14 +6154,6 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6231,20 +6173,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6386,32 +6328,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10859,38 +10801,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDE0FD2B-DE2F-4425-94EA-D67C6058382D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A766C44-7C04-49B0-BD16-188DBCB382FF}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="339">
   <si>
     <t>PRESUPUESTO TOTAL</t>
   </si>
@@ -1045,24 +1045,6 @@
   </si>
   <si>
     <t>Fatima</t>
-  </si>
-  <si>
-    <t>Centro</t>
-  </si>
-  <si>
-    <t>Izp</t>
-  </si>
-  <si>
-    <t>General</t>
-  </si>
-  <si>
-    <t>Hospital</t>
-  </si>
-  <si>
-    <t>Estadio</t>
-  </si>
-  <si>
-    <t>Graderia</t>
   </si>
 </sst>
 </file>
@@ -1513,13 +1495,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5505,251 +5487,76 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="71" t="s">
-        <v>339</v>
-      </c>
-      <c r="B3" s="68">
-        <v>10000</v>
-      </c>
-      <c r="C3" s="69">
-        <v>2000</v>
-      </c>
-      <c r="D3" s="68">
-        <v>5000</v>
-      </c>
-      <c r="E3" s="68">
-        <v>21785.03</v>
-      </c>
-      <c r="F3" s="68">
-        <f t="shared" ref="F3:F10" si="0">C3-D3</f>
-        <v>-3000</v>
-      </c>
-      <c r="G3" s="68">
-        <f t="shared" ref="G3:G10" si="1">C3-E3</f>
-        <v>-19785.03</v>
-      </c>
-      <c r="H3" s="68">
-        <f t="shared" ref="H3:H10" si="2">D3-E3</f>
-        <v>-16785.03</v>
-      </c>
-      <c r="I3" s="72">
-        <f t="shared" ref="I3:I10" si="3">C3/B3</f>
-        <v>0.2</v>
-      </c>
-      <c r="J3" s="72">
-        <f t="shared" ref="J3:J10" si="4">D3/B3</f>
-        <v>0.5</v>
-      </c>
-      <c r="K3" s="68">
-        <f t="shared" ref="K3:K10" si="5">B3-C3</f>
-        <v>8000</v>
-      </c>
+      <c r="A3" s="71"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="72"/>
+      <c r="K3" s="68"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="71" t="s">
-        <v>340</v>
-      </c>
-      <c r="B4" s="68">
-        <v>50000</v>
-      </c>
-      <c r="C4" s="69">
-        <v>25000</v>
-      </c>
-      <c r="D4" s="68">
-        <v>28000</v>
-      </c>
-      <c r="E4" s="68">
-        <v>21786.03</v>
-      </c>
-      <c r="F4" s="68">
-        <f t="shared" si="0"/>
-        <v>-3000</v>
-      </c>
-      <c r="G4" s="68">
-        <f t="shared" si="1"/>
-        <v>3213.9700000000012</v>
-      </c>
-      <c r="H4" s="68">
-        <f t="shared" si="2"/>
-        <v>6213.9700000000012</v>
-      </c>
-      <c r="I4" s="72">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="J4" s="72">
-        <f t="shared" si="4"/>
-        <v>0.56000000000000005</v>
-      </c>
-      <c r="K4" s="68">
-        <f t="shared" si="5"/>
-        <v>25000</v>
-      </c>
+      <c r="A4" s="71"/>
+      <c r="B4" s="68"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="72"/>
+      <c r="K4" s="68"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="71" t="s">
-        <v>341</v>
-      </c>
-      <c r="B5" s="68">
-        <v>25000</v>
-      </c>
-      <c r="C5" s="69">
-        <f>Dashboard!C17</f>
-        <v>17239.126381865146</v>
-      </c>
-      <c r="D5" s="68">
-        <v>20000</v>
-      </c>
-      <c r="E5" s="68">
-        <v>21787.03</v>
-      </c>
-      <c r="F5" s="68">
-        <f t="shared" si="0"/>
-        <v>-2760.873618134854</v>
-      </c>
-      <c r="G5" s="68">
-        <f t="shared" si="1"/>
-        <v>-4547.9036181348529</v>
-      </c>
-      <c r="H5" s="68">
-        <f t="shared" si="2"/>
-        <v>-1787.0299999999988</v>
-      </c>
-      <c r="I5" s="72">
-        <f t="shared" si="3"/>
-        <v>0.68956505527460588</v>
-      </c>
-      <c r="J5" s="72">
-        <f t="shared" si="4"/>
-        <v>0.8</v>
-      </c>
-      <c r="K5" s="68">
-        <f t="shared" si="5"/>
-        <v>7760.873618134854</v>
-      </c>
+      <c r="A5" s="71"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="72"/>
+      <c r="K5" s="68"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="71" t="s">
-        <v>342</v>
-      </c>
-      <c r="B6" s="68">
-        <v>50000</v>
-      </c>
-      <c r="C6" s="69">
-        <v>23000</v>
-      </c>
-      <c r="D6" s="68">
-        <v>30000</v>
-      </c>
-      <c r="E6" s="68">
-        <v>21788.03</v>
-      </c>
-      <c r="F6" s="68">
-        <f t="shared" si="0"/>
-        <v>-7000</v>
-      </c>
-      <c r="G6" s="68">
-        <f t="shared" si="1"/>
-        <v>1211.9700000000012</v>
-      </c>
-      <c r="H6" s="68">
-        <f t="shared" si="2"/>
-        <v>8211.9700000000012</v>
-      </c>
-      <c r="I6" s="72">
-        <f t="shared" si="3"/>
-        <v>0.46</v>
-      </c>
-      <c r="J6" s="72">
-        <f t="shared" si="4"/>
-        <v>0.6</v>
-      </c>
-      <c r="K6" s="68">
-        <f t="shared" si="5"/>
-        <v>27000</v>
-      </c>
+      <c r="A6" s="71"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="72"/>
+      <c r="K6" s="68"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="71" t="s">
-        <v>343</v>
-      </c>
-      <c r="B7" s="68">
-        <v>60000</v>
-      </c>
-      <c r="C7" s="69">
-        <v>12000</v>
-      </c>
-      <c r="D7" s="68">
-        <v>30000</v>
-      </c>
-      <c r="E7" s="68">
-        <v>21789.03</v>
-      </c>
-      <c r="F7" s="68">
-        <f t="shared" si="0"/>
-        <v>-18000</v>
-      </c>
-      <c r="G7" s="68">
-        <f t="shared" si="1"/>
-        <v>-9789.0299999999988</v>
-      </c>
-      <c r="H7" s="68">
-        <f t="shared" si="2"/>
-        <v>8210.9700000000012</v>
-      </c>
-      <c r="I7" s="72">
-        <f t="shared" si="3"/>
-        <v>0.2</v>
-      </c>
-      <c r="J7" s="72">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-      <c r="K7" s="68">
-        <f t="shared" si="5"/>
-        <v>48000</v>
-      </c>
+      <c r="A7" s="71"/>
+      <c r="B7" s="68"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="68"/>
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="72"/>
+      <c r="K7" s="68"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="71" t="s">
-        <v>344</v>
-      </c>
-      <c r="B8" s="68">
-        <v>70000</v>
-      </c>
-      <c r="C8" s="69">
-        <v>35000</v>
-      </c>
-      <c r="D8" s="68">
-        <v>35000</v>
-      </c>
-      <c r="E8" s="68">
-        <v>21790.03</v>
-      </c>
-      <c r="F8" s="68">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G8" s="68">
-        <f t="shared" si="1"/>
-        <v>13209.970000000001</v>
-      </c>
-      <c r="H8" s="68">
-        <f t="shared" si="2"/>
-        <v>13209.970000000001</v>
-      </c>
-      <c r="I8" s="72">
-        <f t="shared" si="3"/>
-        <v>0.5</v>
-      </c>
-      <c r="J8" s="72">
-        <f t="shared" si="4"/>
-        <v>0.5</v>
-      </c>
-      <c r="K8" s="68">
-        <f t="shared" si="5"/>
-        <v>35000</v>
-      </c>
+      <c r="A8" s="71"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="69"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="72"/>
+      <c r="K8" s="68"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="71"/>
@@ -5796,28 +5603,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
@@ -5853,7 +5660,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="74"/>
-      <c r="G5" s="78">
+      <c r="G5" s="76">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5903,7 +5710,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="74"/>
-      <c r="G8" s="78">
+      <c r="G8" s="76">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -6137,14 +5944,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6154,6 +5953,14 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6173,20 +5980,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6328,32 +6135,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10801,38 +10608,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A766C44-7C04-49B0-BD16-188DBCB382FF}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D79CCF4-2A16-4338-A958-1D9E3FC20E0E}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="340">
   <si>
     <t>PRESUPUESTO TOTAL</t>
   </si>
@@ -1045,6 +1045,9 @@
   </si>
   <si>
     <t>Fatima</t>
+  </si>
+  <si>
+    <t>centro</t>
   </si>
 </sst>
 </file>
@@ -1495,13 +1498,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5487,16 +5490,45 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="71"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="72"/>
-      <c r="K3" s="68"/>
+      <c r="A3" s="71" t="s">
+        <v>339</v>
+      </c>
+      <c r="B3" s="68">
+        <v>30000</v>
+      </c>
+      <c r="C3" s="69">
+        <v>10000</v>
+      </c>
+      <c r="D3" s="68">
+        <v>15000</v>
+      </c>
+      <c r="E3" s="68">
+        <v>10000</v>
+      </c>
+      <c r="F3" s="68">
+        <f>C3-D3</f>
+        <v>-5000</v>
+      </c>
+      <c r="G3" s="68">
+        <f>C3-E3</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="68">
+        <f>D3-E3</f>
+        <v>5000</v>
+      </c>
+      <c r="I3" s="72">
+        <f>C3/B3</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J3" s="72">
+        <f>D3/B3</f>
+        <v>0.5</v>
+      </c>
+      <c r="K3" s="68">
+        <f>B3-C3</f>
+        <v>20000</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="71"/>
@@ -5603,28 +5635,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
@@ -5660,7 +5692,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="74"/>
-      <c r="G5" s="76">
+      <c r="G5" s="78">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5710,7 +5742,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="74"/>
-      <c r="G8" s="76">
+      <c r="G8" s="78">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -5944,6 +5976,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -5953,14 +5993,6 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5980,20 +6012,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6135,32 +6167,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10608,38 +10640,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D79CCF4-2A16-4338-A958-1D9E3FC20E0E}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A1FBFC-8755-499E-B164-2C31E1D11C11}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="339">
   <si>
     <t>PRESUPUESTO TOTAL</t>
   </si>
@@ -1045,9 +1045,6 @@
   </si>
   <si>
     <t>Fatima</t>
-  </si>
-  <si>
-    <t>centro</t>
   </si>
 </sst>
 </file>
@@ -1498,13 +1495,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5394,7 +5391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FB8E136-486C-4EB9-920D-6287CDC3043B}">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="32"/>
@@ -5490,45 +5487,16 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="71" t="s">
-        <v>339</v>
-      </c>
-      <c r="B3" s="68">
-        <v>30000</v>
-      </c>
-      <c r="C3" s="69">
-        <v>10000</v>
-      </c>
-      <c r="D3" s="68">
-        <v>15000</v>
-      </c>
-      <c r="E3" s="68">
-        <v>10000</v>
-      </c>
-      <c r="F3" s="68">
-        <f>C3-D3</f>
-        <v>-5000</v>
-      </c>
-      <c r="G3" s="68">
-        <f>C3-E3</f>
-        <v>0</v>
-      </c>
-      <c r="H3" s="68">
-        <f>D3-E3</f>
-        <v>5000</v>
-      </c>
-      <c r="I3" s="72">
-        <f>C3/B3</f>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="J3" s="72">
-        <f>D3/B3</f>
-        <v>0.5</v>
-      </c>
-      <c r="K3" s="68">
-        <f>B3-C3</f>
-        <v>20000</v>
-      </c>
+      <c r="A3" s="71"/>
+      <c r="B3" s="68"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="72"/>
+      <c r="K3" s="68"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="71"/>
@@ -5589,30 +5557,6 @@
       <c r="H8" s="68"/>
       <c r="I8" s="72"/>
       <c r="K8" s="68"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="71"/>
-      <c r="B9" s="68"/>
-      <c r="C9" s="69"/>
-      <c r="D9" s="68"/>
-      <c r="E9" s="68"/>
-      <c r="F9" s="68"/>
-      <c r="G9" s="68"/>
-      <c r="H9" s="68"/>
-      <c r="I9" s="72"/>
-      <c r="K9" s="68"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="71"/>
-      <c r="B10" s="68"/>
-      <c r="C10" s="69"/>
-      <c r="D10" s="68"/>
-      <c r="E10" s="68"/>
-      <c r="F10" s="68"/>
-      <c r="G10" s="68"/>
-      <c r="H10" s="68"/>
-      <c r="I10" s="72"/>
-      <c r="K10" s="68"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5635,28 +5579,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
@@ -5692,7 +5636,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="74"/>
-      <c r="G5" s="78">
+      <c r="G5" s="76">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5742,7 +5686,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="74"/>
-      <c r="G8" s="78">
+      <c r="G8" s="76">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -5976,14 +5920,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -5993,6 +5929,14 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6012,20 +5956,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6167,32 +6111,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10640,38 +10584,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A1FBFC-8755-499E-B164-2C31E1D11C11}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{302E5D02-D1B6-42D4-8255-7491BD4E3A41}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1495,13 +1495,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5451,31 +5451,29 @@
         <v>43821.59</v>
       </c>
       <c r="C2" s="69">
-        <f>Dashboard!C14</f>
-        <v>21784.026381865144</v>
+        <v>21526.560000000001</v>
       </c>
       <c r="D2" s="68">
-        <f>Dashboard!B23</f>
         <v>33203.99</v>
       </c>
       <c r="E2" s="68">
-        <v>21784.03</v>
+        <v>21526.560000000001</v>
       </c>
       <c r="F2" s="68">
         <f>C2-D2</f>
-        <v>-11419.963618134854</v>
+        <v>-11677.429999999997</v>
       </c>
       <c r="G2" s="68">
         <f>C2-E2</f>
-        <v>-3.6181348550599068E-3</v>
+        <v>0</v>
       </c>
       <c r="H2" s="68">
         <f>D2-E2</f>
-        <v>11419.96</v>
+        <v>11677.429999999997</v>
       </c>
       <c r="I2" s="72">
         <f>C2/B2</f>
-        <v>0.49710716525496096</v>
+        <v>0.49123183344100485</v>
       </c>
       <c r="J2" s="72">
         <f>D2/B2</f>
@@ -5483,7 +5481,7 @@
       </c>
       <c r="K2" s="68">
         <f>B2-C2</f>
-        <v>22037.563618134853</v>
+        <v>22295.029999999995</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -5579,28 +5577,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
@@ -5636,7 +5634,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="74"/>
-      <c r="G5" s="76">
+      <c r="G5" s="78">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5686,7 +5684,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="74"/>
-      <c r="G8" s="76">
+      <c r="G8" s="78">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -5920,6 +5918,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -5929,14 +5935,6 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5956,20 +5954,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6111,32 +6109,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10584,38 +10582,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{302E5D02-D1B6-42D4-8255-7491BD4E3A41}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD469077-6112-484E-92EF-88FEE752A4C7}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1495,13 +1495,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5451,17 +5451,18 @@
         <v>43821.59</v>
       </c>
       <c r="C2" s="69">
-        <v>21526.560000000001</v>
+        <v>21795.360000000001</v>
       </c>
       <c r="D2" s="68">
         <v>33203.99</v>
       </c>
       <c r="E2" s="68">
-        <v>21526.560000000001</v>
+        <f>C2</f>
+        <v>21795.360000000001</v>
       </c>
       <c r="F2" s="68">
         <f>C2-D2</f>
-        <v>-11677.429999999997</v>
+        <v>-11408.629999999997</v>
       </c>
       <c r="G2" s="68">
         <f>C2-E2</f>
@@ -5469,11 +5470,11 @@
       </c>
       <c r="H2" s="68">
         <f>D2-E2</f>
-        <v>11677.429999999997</v>
+        <v>11408.629999999997</v>
       </c>
       <c r="I2" s="72">
         <f>C2/B2</f>
-        <v>0.49123183344100485</v>
+        <v>0.49736579617489923</v>
       </c>
       <c r="J2" s="72">
         <f>D2/B2</f>
@@ -5481,7 +5482,7 @@
       </c>
       <c r="K2" s="68">
         <f>B2-C2</f>
-        <v>22295.029999999995</v>
+        <v>22026.229999999996</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -5577,28 +5578,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
@@ -5634,7 +5635,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="74"/>
-      <c r="G5" s="78">
+      <c r="G5" s="76">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5684,7 +5685,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="74"/>
-      <c r="G8" s="78">
+      <c r="G8" s="76">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -5918,14 +5919,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -5935,6 +5928,14 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5954,20 +5955,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6109,32 +6110,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10582,38 +10583,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD469077-6112-484E-92EF-88FEE752A4C7}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFA5189E-7337-44BC-92B4-5DA635F36A25}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1495,13 +1495,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5451,18 +5451,18 @@
         <v>43821.59</v>
       </c>
       <c r="C2" s="69">
-        <v>21795.360000000001</v>
+        <v>21810.36</v>
       </c>
       <c r="D2" s="68">
         <v>33203.99</v>
       </c>
       <c r="E2" s="68">
         <f>C2</f>
-        <v>21795.360000000001</v>
+        <v>21810.36</v>
       </c>
       <c r="F2" s="68">
         <f>C2-D2</f>
-        <v>-11408.629999999997</v>
+        <v>-11393.629999999997</v>
       </c>
       <c r="G2" s="68">
         <f>C2-E2</f>
@@ -5470,11 +5470,11 @@
       </c>
       <c r="H2" s="68">
         <f>D2-E2</f>
-        <v>11408.629999999997</v>
+        <v>11393.629999999997</v>
       </c>
       <c r="I2" s="72">
         <f>C2/B2</f>
-        <v>0.49736579617489923</v>
+        <v>0.49770809320246029</v>
       </c>
       <c r="J2" s="72">
         <f>D2/B2</f>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="K2" s="68">
         <f>B2-C2</f>
-        <v>22026.229999999996</v>
+        <v>22011.229999999996</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -5578,28 +5578,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
@@ -5635,7 +5635,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="74"/>
-      <c r="G5" s="76">
+      <c r="G5" s="78">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5685,7 +5685,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="74"/>
-      <c r="G8" s="76">
+      <c r="G8" s="78">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -5919,6 +5919,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -5928,14 +5936,6 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5955,20 +5955,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6110,32 +6110,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10583,38 +10583,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFA5189E-7337-44BC-92B4-5DA635F36A25}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2517208-8F6D-4289-9DCC-20531A037441}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1495,13 +1495,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5461,8 +5461,8 @@
         <v>21810.36</v>
       </c>
       <c r="F2" s="68">
-        <f>C2-D2</f>
-        <v>-11393.629999999997</v>
+        <f>B2-D2</f>
+        <v>10617.599999999999</v>
       </c>
       <c r="G2" s="68">
         <f>C2-E2</f>
@@ -5578,28 +5578,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
@@ -5635,7 +5635,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="74"/>
-      <c r="G5" s="78">
+      <c r="G5" s="76">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5685,7 +5685,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="74"/>
-      <c r="G8" s="78">
+      <c r="G8" s="76">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -5919,14 +5919,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -5936,6 +5928,14 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5955,20 +5955,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6110,32 +6110,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10583,38 +10583,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2517208-8F6D-4289-9DCC-20531A037441}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B8384F-FEDD-4B93-914B-A2CE1D2CCBD7}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="340">
   <si>
     <t>PRESUPUESTO TOTAL</t>
   </si>
@@ -1045,6 +1045,9 @@
   </si>
   <si>
     <t>Fatima</t>
+  </si>
+  <si>
+    <t>La estancia</t>
   </si>
 </sst>
 </file>
@@ -5486,11 +5489,21 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="71"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
+      <c r="A3" s="71" t="s">
+        <v>339</v>
+      </c>
+      <c r="B3" s="68">
+        <v>0</v>
+      </c>
+      <c r="C3" s="69">
+        <v>0</v>
+      </c>
+      <c r="D3" s="68">
+        <v>0</v>
+      </c>
+      <c r="E3" s="68">
+        <v>0</v>
+      </c>
       <c r="F3" s="68"/>
       <c r="G3" s="68"/>
       <c r="H3" s="68"/>

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79B8384F-FEDD-4B93-914B-A2CE1D2CCBD7}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6346DBA6-7CFA-4729-A5C2-667F0BA344A9}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1498,13 +1498,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5454,14 +5454,14 @@
         <v>43821.59</v>
       </c>
       <c r="C2" s="69">
-        <v>21810.36</v>
+        <v>21951.53</v>
       </c>
       <c r="D2" s="68">
         <v>33203.99</v>
       </c>
       <c r="E2" s="68">
         <f>C2</f>
-        <v>21810.36</v>
+        <v>21951.53</v>
       </c>
       <c r="F2" s="68">
         <f>B2-D2</f>
@@ -5473,11 +5473,11 @@
       </c>
       <c r="H2" s="68">
         <f>D2-E2</f>
-        <v>11393.629999999997</v>
+        <v>11252.46</v>
       </c>
       <c r="I2" s="72">
         <f>C2/B2</f>
-        <v>0.49770809320246029</v>
+        <v>0.50092956462784666</v>
       </c>
       <c r="J2" s="72">
         <f>D2/B2</f>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="K2" s="68">
         <f>B2-C2</f>
-        <v>22011.229999999996</v>
+        <v>21870.059999999998</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -5591,28 +5591,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
@@ -5648,7 +5648,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="74"/>
-      <c r="G5" s="76">
+      <c r="G5" s="78">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5698,7 +5698,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="74"/>
-      <c r="G8" s="76">
+      <c r="G8" s="78">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -5932,6 +5932,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -5941,14 +5949,6 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5968,20 +5968,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6123,32 +6123,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10596,38 +10596,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6346DBA6-7CFA-4729-A5C2-667F0BA344A9}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200CF074-4192-40DD-889F-520E613F0BF0}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-5475" yWindow="915" windowWidth="13740" windowHeight="7770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen Financiero" sheetId="9" r:id="rId1"/>
@@ -1498,13 +1498,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5450,22 +5450,21 @@
         <v>338</v>
       </c>
       <c r="B2" s="68">
-        <f>Presupuesto!E11</f>
-        <v>43821.59</v>
+        <v>38605.82</v>
       </c>
       <c r="C2" s="69">
-        <v>21951.53</v>
+        <v>23177.53</v>
       </c>
       <c r="D2" s="68">
         <v>33203.99</v>
       </c>
       <c r="E2" s="68">
         <f>C2</f>
-        <v>21951.53</v>
+        <v>23177.53</v>
       </c>
       <c r="F2" s="68">
         <f>B2-D2</f>
-        <v>10617.599999999999</v>
+        <v>5401.8300000000017</v>
       </c>
       <c r="G2" s="68">
         <f>C2-E2</f>
@@ -5473,19 +5472,19 @@
       </c>
       <c r="H2" s="68">
         <f>D2-E2</f>
-        <v>11252.46</v>
+        <v>10026.459999999999</v>
       </c>
       <c r="I2" s="72">
         <f>C2/B2</f>
-        <v>0.50092956462784666</v>
+        <v>0.60036362393027787</v>
       </c>
       <c r="J2" s="72">
         <f>D2/B2</f>
-        <v>0.75770847201117075</v>
+        <v>0.8600773147675661</v>
       </c>
       <c r="K2" s="68">
         <f>B2-C2</f>
-        <v>21870.059999999998</v>
+        <v>15428.29</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -5591,28 +5590,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
@@ -5648,7 +5647,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="74"/>
-      <c r="G5" s="78">
+      <c r="G5" s="76">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5698,7 +5697,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="74"/>
-      <c r="G8" s="78">
+      <c r="G8" s="76">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -5932,14 +5931,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -5949,6 +5940,14 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5968,20 +5967,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6123,32 +6122,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10596,38 +10595,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200CF074-4192-40DD-889F-520E613F0BF0}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08B9C6F-B14F-4008-8677-6CE3D539B895}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5475" yWindow="915" windowWidth="13740" windowHeight="7770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen Financiero" sheetId="9" r:id="rId1"/>
@@ -1498,13 +1498,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -2700,7 +2700,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="es-CO"/>
+          <a:endParaRPr lang="es-VE"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2798,7 +2798,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="es-CO"/>
+                <a:endParaRPr lang="es-VE"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="outEnd"/>
@@ -2950,7 +2950,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="es-CO"/>
+                <a:endParaRPr lang="es-VE"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="outEnd"/>
@@ -3069,7 +3069,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-CO"/>
+            <a:endParaRPr lang="es-VE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="100"/>
@@ -3127,7 +3127,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-CO"/>
+            <a:endParaRPr lang="es-VE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="10"/>
@@ -3179,7 +3179,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="es-CO"/>
+      <a:endParaRPr lang="es-VE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -3272,7 +3272,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="es-CO"/>
+          <a:endParaRPr lang="es-VE"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -3370,7 +3370,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="es-CO"/>
+                <a:endParaRPr lang="es-VE"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="outEnd"/>
@@ -3522,7 +3522,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="es-CO"/>
+                <a:endParaRPr lang="es-VE"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="outEnd"/>
@@ -3641,7 +3641,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-CO"/>
+            <a:endParaRPr lang="es-VE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="616260688"/>
@@ -3699,7 +3699,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="es-CO"/>
+            <a:endParaRPr lang="es-VE"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="616265680"/>
@@ -3740,7 +3740,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="es-CO"/>
+          <a:endParaRPr lang="es-VE"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -3781,7 +3781,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="es-CO"/>
+      <a:endParaRPr lang="es-VE"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -5453,14 +5453,14 @@
         <v>38605.82</v>
       </c>
       <c r="C2" s="69">
-        <v>23177.53</v>
+        <v>23285.99</v>
       </c>
       <c r="D2" s="68">
         <v>33203.99</v>
       </c>
       <c r="E2" s="68">
         <f>C2</f>
-        <v>23177.53</v>
+        <v>23285.99</v>
       </c>
       <c r="F2" s="68">
         <f>B2-D2</f>
@@ -5472,11 +5472,11 @@
       </c>
       <c r="H2" s="68">
         <f>D2-E2</f>
-        <v>10026.459999999999</v>
+        <v>9917.9999999999964</v>
       </c>
       <c r="I2" s="72">
         <f>C2/B2</f>
-        <v>0.60036362393027787</v>
+        <v>0.6031730448932312</v>
       </c>
       <c r="J2" s="72">
         <f>D2/B2</f>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="K2" s="68">
         <f>B2-C2</f>
-        <v>15428.29</v>
+        <v>15319.829999999998</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -5590,28 +5590,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
@@ -5647,7 +5647,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="74"/>
-      <c r="G5" s="76">
+      <c r="G5" s="78">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5697,7 +5697,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="74"/>
-      <c r="G8" s="76">
+      <c r="G8" s="78">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -5931,6 +5931,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -5940,14 +5948,6 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5967,20 +5967,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6122,32 +6122,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10595,38 +10595,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08B9C6F-B14F-4008-8677-6CE3D539B895}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C34C0EDC-B306-47A7-B3F6-2F6CD1E18B85}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <sheet name="Nomina" sheetId="5" r:id="rId8"/>
     <sheet name="Calculos" sheetId="6" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -5459,8 +5459,8 @@
         <v>33203.99</v>
       </c>
       <c r="E2" s="68">
-        <f>C2</f>
-        <v>23285.99</v>
+        <f>D2-C2</f>
+        <v>9917.9999999999964</v>
       </c>
       <c r="F2" s="68">
         <f>B2-D2</f>
@@ -5468,10 +5468,10 @@
       </c>
       <c r="G2" s="68">
         <f>C2-E2</f>
-        <v>0</v>
+        <v>13367.990000000005</v>
       </c>
       <c r="H2" s="68">
-        <f>D2-E2</f>
+        <f>E2</f>
         <v>9917.9999999999964</v>
       </c>
       <c r="I2" s="72">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C34C0EDC-B306-47A7-B3F6-2F6CD1E18B85}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0865A2B2-09E3-422C-ABF0-0E953D2C15EE}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <sheet name="Nomina" sheetId="5" r:id="rId8"/>
     <sheet name="Calculos" sheetId="6" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="181029" iterateDelta="1E-4"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -1498,13 +1498,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5453,14 +5453,14 @@
         <v>38605.82</v>
       </c>
       <c r="C2" s="69">
-        <v>23285.99</v>
+        <v>24894.53</v>
       </c>
       <c r="D2" s="68">
         <v>33203.99</v>
       </c>
       <c r="E2" s="68">
         <f>D2-C2</f>
-        <v>9917.9999999999964</v>
+        <v>8309.4599999999991</v>
       </c>
       <c r="F2" s="68">
         <f>B2-D2</f>
@@ -5468,15 +5468,15 @@
       </c>
       <c r="G2" s="68">
         <f>C2-E2</f>
-        <v>13367.990000000005</v>
+        <v>16585.07</v>
       </c>
       <c r="H2" s="68">
         <f>E2</f>
-        <v>9917.9999999999964</v>
+        <v>8309.4599999999991</v>
       </c>
       <c r="I2" s="72">
         <f>C2/B2</f>
-        <v>0.6031730448932312</v>
+        <v>0.6448387833751491</v>
       </c>
       <c r="J2" s="72">
         <f>D2/B2</f>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="K2" s="68">
         <f>B2-C2</f>
-        <v>15319.829999999998</v>
+        <v>13711.29</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -5590,28 +5590,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
@@ -5647,7 +5647,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="74"/>
-      <c r="G5" s="78">
+      <c r="G5" s="76">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5697,7 +5697,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="74"/>
-      <c r="G8" s="78">
+      <c r="G8" s="76">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -5931,14 +5931,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -5948,6 +5940,14 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5967,20 +5967,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6122,32 +6122,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10595,38 +10595,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0865A2B2-09E3-422C-ABF0-0E953D2C15EE}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E231EFA6-2B7B-4687-83ED-2372C09D432B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1498,13 +1498,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5453,14 +5453,14 @@
         <v>38605.82</v>
       </c>
       <c r="C2" s="69">
-        <v>24894.53</v>
+        <v>25164.53</v>
       </c>
       <c r="D2" s="68">
         <v>33203.99</v>
       </c>
       <c r="E2" s="68">
         <f>D2-C2</f>
-        <v>8309.4599999999991</v>
+        <v>8039.4599999999991</v>
       </c>
       <c r="F2" s="68">
         <f>B2-D2</f>
@@ -5468,15 +5468,15 @@
       </c>
       <c r="G2" s="68">
         <f>C2-E2</f>
-        <v>16585.07</v>
+        <v>17125.07</v>
       </c>
       <c r="H2" s="68">
         <f>E2</f>
-        <v>8309.4599999999991</v>
+        <v>8039.4599999999991</v>
       </c>
       <c r="I2" s="72">
         <f>C2/B2</f>
-        <v>0.6448387833751491</v>
+        <v>0.65183254752780795</v>
       </c>
       <c r="J2" s="72">
         <f>D2/B2</f>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="K2" s="68">
         <f>B2-C2</f>
-        <v>13711.29</v>
+        <v>13441.29</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -5590,28 +5590,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
@@ -5647,7 +5647,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="74"/>
-      <c r="G5" s="76">
+      <c r="G5" s="78">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5697,7 +5697,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="74"/>
-      <c r="G8" s="76">
+      <c r="G8" s="78">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -5931,6 +5931,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -5940,14 +5948,6 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5967,20 +5967,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6122,32 +6122,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10595,38 +10595,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E231EFA6-2B7B-4687-83ED-2372C09D432B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35BBF736-9D93-4F7F-97A7-42633A96837A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-6435" yWindow="750" windowWidth="13740" windowHeight="7770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen Financiero" sheetId="9" r:id="rId1"/>
@@ -1498,13 +1498,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5456,23 +5456,23 @@
         <v>25164.53</v>
       </c>
       <c r="D2" s="68">
-        <v>33203.99</v>
+        <v>36592.22</v>
       </c>
       <c r="E2" s="68">
         <f>D2-C2</f>
-        <v>8039.4599999999991</v>
+        <v>11427.690000000002</v>
       </c>
       <c r="F2" s="68">
         <f>B2-D2</f>
-        <v>5401.8300000000017</v>
+        <v>2013.5999999999985</v>
       </c>
       <c r="G2" s="68">
         <f>C2-E2</f>
-        <v>17125.07</v>
+        <v>13736.839999999997</v>
       </c>
       <c r="H2" s="68">
         <f>E2</f>
-        <v>8039.4599999999991</v>
+        <v>11427.690000000002</v>
       </c>
       <c r="I2" s="72">
         <f>C2/B2</f>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="J2" s="72">
         <f>D2/B2</f>
-        <v>0.8600773147675661</v>
+        <v>0.94784206111928204</v>
       </c>
       <c r="K2" s="68">
         <f>B2-C2</f>
@@ -5590,28 +5590,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
@@ -5647,7 +5647,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="74"/>
-      <c r="G5" s="78">
+      <c r="G5" s="76">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5697,7 +5697,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="74"/>
-      <c r="G8" s="78">
+      <c r="G8" s="76">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -5931,14 +5931,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -5948,6 +5940,14 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5967,20 +5967,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6122,32 +6122,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10595,38 +10595,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35BBF736-9D93-4F7F-97A7-42633A96837A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC6E554D-D783-4871-9B68-E715E0288721}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-6435" yWindow="750" windowWidth="13740" windowHeight="7770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen Financiero" sheetId="9" r:id="rId1"/>
@@ -1498,13 +1498,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5453,14 +5453,14 @@
         <v>38605.82</v>
       </c>
       <c r="C2" s="69">
-        <v>25164.53</v>
+        <v>19034.740000000002</v>
       </c>
       <c r="D2" s="68">
         <v>36592.22</v>
       </c>
       <c r="E2" s="68">
         <f>D2-C2</f>
-        <v>11427.690000000002</v>
+        <v>17557.48</v>
       </c>
       <c r="F2" s="68">
         <f>B2-D2</f>
@@ -5468,15 +5468,15 @@
       </c>
       <c r="G2" s="68">
         <f>C2-E2</f>
-        <v>13736.839999999997</v>
+        <v>1477.260000000002</v>
       </c>
       <c r="H2" s="68">
         <f>E2</f>
-        <v>11427.690000000002</v>
+        <v>17557.48</v>
       </c>
       <c r="I2" s="72">
         <f>C2/B2</f>
-        <v>0.65183254752780795</v>
+        <v>0.49305363802659813</v>
       </c>
       <c r="J2" s="72">
         <f>D2/B2</f>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="K2" s="68">
         <f>B2-C2</f>
-        <v>13441.29</v>
+        <v>19571.079999999998</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -5590,28 +5590,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
@@ -5647,7 +5647,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="74"/>
-      <c r="G5" s="76">
+      <c r="G5" s="78">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5697,7 +5697,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="74"/>
-      <c r="G8" s="76">
+      <c r="G8" s="78">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -5931,6 +5931,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -5940,14 +5948,6 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5967,20 +5967,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6122,32 +6122,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10595,38 +10595,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC6E554D-D783-4871-9B68-E715E0288721}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69CCE620-8AE3-4D09-8C83-41FACB976B22}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1498,13 +1498,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5453,14 +5453,14 @@
         <v>38605.82</v>
       </c>
       <c r="C2" s="69">
-        <v>19034.740000000002</v>
+        <v>21903.94</v>
       </c>
       <c r="D2" s="68">
         <v>36592.22</v>
       </c>
       <c r="E2" s="68">
         <f>D2-C2</f>
-        <v>17557.48</v>
+        <v>14688.280000000002</v>
       </c>
       <c r="F2" s="68">
         <f>B2-D2</f>
@@ -5468,15 +5468,15 @@
       </c>
       <c r="G2" s="68">
         <f>C2-E2</f>
-        <v>1477.260000000002</v>
+        <v>7215.6599999999962</v>
       </c>
       <c r="H2" s="68">
         <f>E2</f>
-        <v>17557.48</v>
+        <v>14688.280000000002</v>
       </c>
       <c r="I2" s="72">
         <f>C2/B2</f>
-        <v>0.49305363802659813</v>
+        <v>0.56737403842218603</v>
       </c>
       <c r="J2" s="72">
         <f>D2/B2</f>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="K2" s="68">
         <f>B2-C2</f>
-        <v>19571.079999999998</v>
+        <v>16701.88</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -5590,28 +5590,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
@@ -5647,7 +5647,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="74"/>
-      <c r="G5" s="78">
+      <c r="G5" s="76">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5697,7 +5697,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="74"/>
-      <c r="G8" s="78">
+      <c r="G8" s="76">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -5931,14 +5931,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -5948,6 +5940,14 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5967,20 +5967,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6122,32 +6122,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10595,38 +10595,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69CCE620-8AE3-4D09-8C83-41FACB976B22}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AAAF3C2-530B-4A25-B1B1-DCE1B52A4EA4}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1498,13 +1498,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5456,23 +5456,23 @@
         <v>21903.94</v>
       </c>
       <c r="D2" s="68">
-        <v>36592.22</v>
+        <v>36461.21</v>
       </c>
       <c r="E2" s="68">
         <f>D2-C2</f>
-        <v>14688.280000000002</v>
+        <v>14557.27</v>
       </c>
       <c r="F2" s="68">
         <f>B2-D2</f>
-        <v>2013.5999999999985</v>
+        <v>2144.6100000000006</v>
       </c>
       <c r="G2" s="68">
         <f>C2-E2</f>
-        <v>7215.6599999999962</v>
+        <v>7346.6699999999983</v>
       </c>
       <c r="H2" s="68">
         <f>E2</f>
-        <v>14688.280000000002</v>
+        <v>14557.27</v>
       </c>
       <c r="I2" s="72">
         <f>C2/B2</f>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="J2" s="72">
         <f>D2/B2</f>
-        <v>0.94784206111928204</v>
+        <v>0.94444853133543072</v>
       </c>
       <c r="K2" s="68">
         <f>B2-C2</f>
@@ -5590,28 +5590,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
@@ -5647,7 +5647,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="74"/>
-      <c r="G5" s="76">
+      <c r="G5" s="78">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5697,7 +5697,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="74"/>
-      <c r="G8" s="76">
+      <c r="G8" s="78">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -5931,6 +5931,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -5940,14 +5948,6 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5967,20 +5967,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6122,32 +6122,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10595,38 +10595,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AAAF3C2-530B-4A25-B1B1-DCE1B52A4EA4}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFA2ED4-187F-4672-94F8-DFB0CA17DEC5}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1047,7 +1047,7 @@
     <t>Fatima</t>
   </si>
   <si>
-    <t>La estancia</t>
+    <t>Sólo Fatima</t>
   </si>
 </sst>
 </file>
@@ -5492,22 +5492,42 @@
         <v>339</v>
       </c>
       <c r="B3" s="68">
-        <v>0</v>
+        <v>38605.82</v>
       </c>
       <c r="C3" s="69">
-        <v>0</v>
+        <v>18550.72</v>
       </c>
       <c r="D3" s="68">
-        <v>0</v>
+        <v>36461.21</v>
       </c>
       <c r="E3" s="68">
-        <v>0</v>
-      </c>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="72"/>
-      <c r="K3" s="68"/>
+        <f>D3-C3</f>
+        <v>17910.489999999998</v>
+      </c>
+      <c r="F3" s="68">
+        <f>B3-D3</f>
+        <v>2144.6100000000006</v>
+      </c>
+      <c r="G3" s="68">
+        <f>C3-E3</f>
+        <v>640.2300000000032</v>
+      </c>
+      <c r="H3" s="68">
+        <f>E3</f>
+        <v>17910.489999999998</v>
+      </c>
+      <c r="I3" s="72">
+        <f>C3/B3</f>
+        <v>0.48051615015559834</v>
+      </c>
+      <c r="J3" s="72">
+        <f>D3/B3</f>
+        <v>0.94444853133543072</v>
+      </c>
+      <c r="K3" s="68">
+        <f>B3-C3</f>
+        <v>20055.099999999999</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="71"/>

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFA2ED4-187F-4672-94F8-DFB0CA17DEC5}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E1DD76D-1190-4EEA-B8A7-E3BEAC3AA7BA}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1044,10 +1044,10 @@
     <t>Obra</t>
   </si>
   <si>
-    <t>Fatima</t>
-  </si>
-  <si>
-    <t>Sólo Fatima</t>
+    <t>Fatima Real</t>
+  </si>
+  <si>
+    <t>Fatima Full</t>
   </si>
 </sst>
 </file>
@@ -1498,13 +1498,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5447,20 +5447,20 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="71" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B2" s="68">
         <v>38605.82</v>
       </c>
       <c r="C2" s="69">
-        <v>21903.94</v>
+        <v>22382.78</v>
       </c>
       <c r="D2" s="68">
         <v>36461.21</v>
       </c>
       <c r="E2" s="68">
         <f>D2-C2</f>
-        <v>14557.27</v>
+        <v>14078.43</v>
       </c>
       <c r="F2" s="68">
         <f>B2-D2</f>
@@ -5468,15 +5468,15 @@
       </c>
       <c r="G2" s="68">
         <f>C2-E2</f>
-        <v>7346.6699999999983</v>
+        <v>8304.3499999999985</v>
       </c>
       <c r="H2" s="68">
         <f>E2</f>
-        <v>14557.27</v>
+        <v>14078.43</v>
       </c>
       <c r="I2" s="72">
         <f>C2/B2</f>
-        <v>0.56737403842218603</v>
+        <v>0.5797773496327755</v>
       </c>
       <c r="J2" s="72">
         <f>D2/B2</f>
@@ -5484,25 +5484,25 @@
       </c>
       <c r="K2" s="68">
         <f>B2-C2</f>
-        <v>16701.88</v>
+        <v>16223.04</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="71" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B3" s="68">
         <v>38605.82</v>
       </c>
       <c r="C3" s="69">
-        <v>18550.72</v>
+        <v>19029</v>
       </c>
       <c r="D3" s="68">
         <v>36461.21</v>
       </c>
       <c r="E3" s="68">
         <f>D3-C3</f>
-        <v>17910.489999999998</v>
+        <v>17432.21</v>
       </c>
       <c r="F3" s="68">
         <f>B3-D3</f>
@@ -5510,15 +5510,15 @@
       </c>
       <c r="G3" s="68">
         <f>C3-E3</f>
-        <v>640.2300000000032</v>
+        <v>1596.7900000000009</v>
       </c>
       <c r="H3" s="68">
         <f>E3</f>
-        <v>17910.489999999998</v>
+        <v>17432.21</v>
       </c>
       <c r="I3" s="72">
         <f>C3/B3</f>
-        <v>0.48051615015559834</v>
+        <v>0.49290495578127858</v>
       </c>
       <c r="J3" s="72">
         <f>D3/B3</f>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="K3" s="68">
         <f>B3-C3</f>
-        <v>20055.099999999999</v>
+        <v>19576.82</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -5610,28 +5610,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
@@ -5667,7 +5667,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="74"/>
-      <c r="G5" s="78">
+      <c r="G5" s="76">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5717,7 +5717,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="74"/>
-      <c r="G8" s="78">
+      <c r="G8" s="76">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -5951,14 +5951,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -5968,6 +5960,14 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -5987,20 +5987,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6142,32 +6142,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10615,38 +10615,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E1DD76D-1190-4EEA-B8A7-E3BEAC3AA7BA}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{778FB0F5-EB2B-4D84-8484-99CCE35A7624}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="341">
   <si>
     <t>PRESUPUESTO TOTAL</t>
   </si>
@@ -1048,6 +1048,9 @@
   </si>
   <si>
     <t>Fatima Full</t>
+  </si>
+  <si>
+    <t>La Estancia</t>
   </si>
 </sst>
 </file>
@@ -5453,14 +5456,14 @@
         <v>38605.82</v>
       </c>
       <c r="C2" s="69">
-        <v>22382.78</v>
+        <v>22416.78</v>
       </c>
       <c r="D2" s="68">
         <v>36461.21</v>
       </c>
       <c r="E2" s="68">
         <f>D2-C2</f>
-        <v>14078.43</v>
+        <v>14044.43</v>
       </c>
       <c r="F2" s="68">
         <f>B2-D2</f>
@@ -5468,15 +5471,15 @@
       </c>
       <c r="G2" s="68">
         <f>C2-E2</f>
-        <v>8304.3499999999985</v>
+        <v>8372.3499999999985</v>
       </c>
       <c r="H2" s="68">
         <f>E2</f>
-        <v>14078.43</v>
+        <v>14044.43</v>
       </c>
       <c r="I2" s="72">
         <f>C2/B2</f>
-        <v>0.5797773496327755</v>
+        <v>0.58065804585940661</v>
       </c>
       <c r="J2" s="72">
         <f>D2/B2</f>
@@ -5484,7 +5487,7 @@
       </c>
       <c r="K2" s="68">
         <f>B2-C2</f>
-        <v>16223.04</v>
+        <v>16189.04</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -5495,14 +5498,14 @@
         <v>38605.82</v>
       </c>
       <c r="C3" s="69">
-        <v>19029</v>
+        <v>19063.55</v>
       </c>
       <c r="D3" s="68">
         <v>36461.21</v>
       </c>
       <c r="E3" s="68">
         <f>D3-C3</f>
-        <v>17432.21</v>
+        <v>17397.66</v>
       </c>
       <c r="F3" s="68">
         <f>B3-D3</f>
@@ -5510,15 +5513,15 @@
       </c>
       <c r="G3" s="68">
         <f>C3-E3</f>
-        <v>1596.7900000000009</v>
+        <v>1665.8899999999994</v>
       </c>
       <c r="H3" s="68">
         <f>E3</f>
-        <v>17432.21</v>
+        <v>17397.66</v>
       </c>
       <c r="I3" s="72">
         <f>C3/B3</f>
-        <v>0.49290495578127858</v>
+        <v>0.49379989856451695</v>
       </c>
       <c r="J3" s="72">
         <f>D3/B3</f>
@@ -5526,20 +5529,50 @@
       </c>
       <c r="K3" s="68">
         <f>B3-C3</f>
-        <v>19576.82</v>
+        <v>19542.27</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="71"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="72"/>
-      <c r="K4" s="68"/>
+      <c r="A4" s="71" t="s">
+        <v>340</v>
+      </c>
+      <c r="B4" s="68">
+        <v>10524</v>
+      </c>
+      <c r="C4" s="69">
+        <v>0</v>
+      </c>
+      <c r="D4" s="68">
+        <v>0</v>
+      </c>
+      <c r="E4" s="68">
+        <f>D4-C4</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="68">
+        <f>B4-D4</f>
+        <v>10524</v>
+      </c>
+      <c r="G4" s="68">
+        <f>C4-E4</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="68">
+        <f>E4</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="72">
+        <f>C4/B4</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="72">
+        <f>D4/B4</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="68">
+        <f>B4-C4</f>
+        <v>10524</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="71"/>

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{778FB0F5-EB2B-4D84-8484-99CCE35A7624}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C07508-B5EF-47C3-82B0-72EC81B254C5}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-6855" yWindow="2385" windowWidth="13740" windowHeight="7770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen Financiero" sheetId="9" r:id="rId1"/>
@@ -1501,13 +1501,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5456,30 +5456,30 @@
         <v>38605.82</v>
       </c>
       <c r="C2" s="69">
-        <v>22416.78</v>
+        <v>22429.07</v>
       </c>
       <c r="D2" s="68">
         <v>36461.21</v>
       </c>
       <c r="E2" s="68">
         <f>D2-C2</f>
-        <v>14044.43</v>
+        <v>14032.14</v>
       </c>
       <c r="F2" s="68">
-        <f>B2-D2</f>
+        <f t="shared" ref="F2:G4" si="0">B2-D2</f>
         <v>2144.6100000000006</v>
       </c>
       <c r="G2" s="68">
-        <f>C2-E2</f>
-        <v>8372.3499999999985</v>
+        <f t="shared" si="0"/>
+        <v>8396.93</v>
       </c>
       <c r="H2" s="68">
         <f>E2</f>
-        <v>14044.43</v>
+        <v>14032.14</v>
       </c>
       <c r="I2" s="72">
         <f>C2/B2</f>
-        <v>0.58065804585940661</v>
+        <v>0.58097639164250359</v>
       </c>
       <c r="J2" s="72">
         <f>D2/B2</f>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="K2" s="68">
         <f>B2-C2</f>
-        <v>16189.04</v>
+        <v>16176.75</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -5498,30 +5498,30 @@
         <v>38605.82</v>
       </c>
       <c r="C3" s="69">
-        <v>19063.55</v>
+        <v>19075.849999999999</v>
       </c>
       <c r="D3" s="68">
         <v>36461.21</v>
       </c>
       <c r="E3" s="68">
         <f>D3-C3</f>
-        <v>17397.66</v>
+        <v>17385.36</v>
       </c>
       <c r="F3" s="68">
-        <f>B3-D3</f>
+        <f t="shared" si="0"/>
         <v>2144.6100000000006</v>
       </c>
       <c r="G3" s="68">
-        <f>C3-E3</f>
-        <v>1665.8899999999994</v>
+        <f t="shared" si="0"/>
+        <v>1690.489999999998</v>
       </c>
       <c r="H3" s="68">
         <f>E3</f>
-        <v>17397.66</v>
+        <v>17385.36</v>
       </c>
       <c r="I3" s="72">
         <f>C3/B3</f>
-        <v>0.49379989856451695</v>
+        <v>0.49411850337591584</v>
       </c>
       <c r="J3" s="72">
         <f>D3/B3</f>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="K3" s="68">
         <f>B3-C3</f>
-        <v>19542.27</v>
+        <v>19529.97</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -5550,11 +5550,11 @@
         <v>0</v>
       </c>
       <c r="F4" s="68">
-        <f>B4-D4</f>
+        <f t="shared" si="0"/>
         <v>10524</v>
       </c>
       <c r="G4" s="68">
-        <f>C4-E4</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H4" s="68">
@@ -5643,28 +5643,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
@@ -5700,7 +5700,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="74"/>
-      <c r="G5" s="76">
+      <c r="G5" s="78">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5750,7 +5750,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="74"/>
-      <c r="G8" s="76">
+      <c r="G8" s="78">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -5984,6 +5984,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -5993,14 +6001,6 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6020,20 +6020,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6175,32 +6175,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10648,38 +10648,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C07508-B5EF-47C3-82B0-72EC81B254C5}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB83F795-AB9B-47C9-B733-3831421376C0}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-6855" yWindow="2385" windowWidth="13740" windowHeight="7770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen Financiero" sheetId="9" r:id="rId1"/>
@@ -1501,13 +1501,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5456,14 +5456,14 @@
         <v>38605.82</v>
       </c>
       <c r="C2" s="69">
-        <v>22429.07</v>
+        <v>24417.41</v>
       </c>
       <c r="D2" s="68">
         <v>36461.21</v>
       </c>
       <c r="E2" s="68">
         <f>D2-C2</f>
-        <v>14032.14</v>
+        <v>12043.8</v>
       </c>
       <c r="F2" s="68">
         <f t="shared" ref="F2:G4" si="0">B2-D2</f>
@@ -5471,15 +5471,15 @@
       </c>
       <c r="G2" s="68">
         <f t="shared" si="0"/>
-        <v>8396.93</v>
+        <v>12373.61</v>
       </c>
       <c r="H2" s="68">
         <f>E2</f>
-        <v>14032.14</v>
+        <v>12043.8</v>
       </c>
       <c r="I2" s="72">
         <f>C2/B2</f>
-        <v>0.58097639164250359</v>
+        <v>0.63248002503249512</v>
       </c>
       <c r="J2" s="72">
         <f>D2/B2</f>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="K2" s="68">
         <f>B2-C2</f>
-        <v>16176.75</v>
+        <v>14188.41</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -5498,14 +5498,14 @@
         <v>38605.82</v>
       </c>
       <c r="C3" s="69">
-        <v>19075.849999999999</v>
+        <v>21064.19</v>
       </c>
       <c r="D3" s="68">
         <v>36461.21</v>
       </c>
       <c r="E3" s="68">
         <f>D3-C3</f>
-        <v>17385.36</v>
+        <v>15397.02</v>
       </c>
       <c r="F3" s="68">
         <f t="shared" si="0"/>
@@ -5513,15 +5513,15 @@
       </c>
       <c r="G3" s="68">
         <f t="shared" si="0"/>
-        <v>1690.489999999998</v>
+        <v>5667.1699999999983</v>
       </c>
       <c r="H3" s="68">
         <f>E3</f>
-        <v>17385.36</v>
+        <v>15397.02</v>
       </c>
       <c r="I3" s="72">
         <f>C3/B3</f>
-        <v>0.49411850337591584</v>
+        <v>0.54562213676590732</v>
       </c>
       <c r="J3" s="72">
         <f>D3/B3</f>
@@ -5529,7 +5529,7 @@
       </c>
       <c r="K3" s="68">
         <f>B3-C3</f>
-        <v>19529.97</v>
+        <v>17541.63</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -5643,28 +5643,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
@@ -5700,7 +5700,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="74"/>
-      <c r="G5" s="78">
+      <c r="G5" s="76">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5750,7 +5750,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="74"/>
-      <c r="G8" s="78">
+      <c r="G8" s="76">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -5984,14 +5984,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6001,6 +5993,14 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6020,20 +6020,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6175,32 +6175,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10648,38 +10648,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB83F795-AB9B-47C9-B733-3831421376C0}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B9AACA9-AE30-48FC-87D2-EE6E4C127361}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="345">
   <si>
     <t>PRESUPUESTO TOTAL</t>
   </si>
@@ -1044,13 +1044,25 @@
     <t>Obra</t>
   </si>
   <si>
-    <t>Fatima Real</t>
-  </si>
-  <si>
-    <t>Fatima Full</t>
-  </si>
-  <si>
-    <t>La Estancia</t>
+    <t xml:space="preserve">FATIMA  </t>
+  </si>
+  <si>
+    <t>CACUTE SUELOS CAFÉ</t>
+  </si>
+  <si>
+    <t>CACUTE SUELOS GALPON</t>
+  </si>
+  <si>
+    <t>ESTANCIA 2ET</t>
+  </si>
+  <si>
+    <t>ESTANCIA ELECTRODOMESTICOS</t>
+  </si>
+  <si>
+    <t>ESTANCIA LENCERIA</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
   </si>
 </sst>
 </file>
@@ -1501,13 +1513,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5400,7 +5412,7 @@
   <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="32"/>
+    <col min="1" max="1" width="12.85546875" style="32" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" style="32" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.7109375" style="32" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="33.42578125" style="32" bestFit="1" customWidth="1"/>
@@ -5450,86 +5462,86 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="71" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B2" s="68">
-        <v>38605.82</v>
+        <v>39324.74</v>
       </c>
       <c r="C2" s="69">
-        <v>24417.41</v>
+        <v>22770.240000000002</v>
       </c>
       <c r="D2" s="68">
-        <v>36461.21</v>
+        <v>39324.74</v>
       </c>
       <c r="E2" s="68">
         <f>D2-C2</f>
-        <v>12043.8</v>
+        <v>16554.499999999996</v>
       </c>
       <c r="F2" s="68">
         <f t="shared" ref="F2:G4" si="0">B2-D2</f>
-        <v>2144.6100000000006</v>
+        <v>0</v>
       </c>
       <c r="G2" s="68">
         <f t="shared" si="0"/>
-        <v>12373.61</v>
+        <v>6215.7400000000052</v>
       </c>
       <c r="H2" s="68">
         <f>E2</f>
-        <v>12043.8</v>
+        <v>16554.499999999996</v>
       </c>
       <c r="I2" s="72">
         <f>C2/B2</f>
-        <v>0.63248002503249512</v>
+        <v>0.57903091031243947</v>
       </c>
       <c r="J2" s="72">
         <f>D2/B2</f>
-        <v>0.94444853133543072</v>
+        <v>1</v>
       </c>
       <c r="K2" s="68">
         <f>B2-C2</f>
-        <v>14188.41</v>
+        <v>16554.499999999996</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="71" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B3" s="68">
-        <v>38605.82</v>
+        <v>580</v>
       </c>
       <c r="C3" s="69">
-        <v>21064.19</v>
+        <v>315</v>
       </c>
       <c r="D3" s="68">
-        <v>36461.21</v>
+        <v>406</v>
       </c>
       <c r="E3" s="68">
         <f>D3-C3</f>
-        <v>15397.02</v>
+        <v>91</v>
       </c>
       <c r="F3" s="68">
         <f t="shared" si="0"/>
-        <v>2144.6100000000006</v>
+        <v>174</v>
       </c>
       <c r="G3" s="68">
         <f t="shared" si="0"/>
-        <v>5667.1699999999983</v>
+        <v>224</v>
       </c>
       <c r="H3" s="68">
         <f>E3</f>
-        <v>15397.02</v>
+        <v>91</v>
       </c>
       <c r="I3" s="72">
         <f>C3/B3</f>
-        <v>0.54562213676590732</v>
+        <v>0.5431034482758621</v>
       </c>
       <c r="J3" s="72">
         <f>D3/B3</f>
-        <v>0.94444853133543072</v>
+        <v>0.7</v>
       </c>
       <c r="K3" s="68">
         <f>B3-C3</f>
-        <v>17541.63</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -5537,47 +5549,53 @@
         <v>340</v>
       </c>
       <c r="B4" s="68">
-        <v>10524</v>
+        <v>580</v>
       </c>
       <c r="C4" s="69">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="D4" s="68">
-        <v>0</v>
+        <v>406</v>
       </c>
       <c r="E4" s="68">
         <f>D4-C4</f>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="F4" s="68">
         <f t="shared" si="0"/>
-        <v>10524</v>
+        <v>174</v>
       </c>
       <c r="G4" s="68">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="H4" s="68">
         <f>E4</f>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="I4" s="72">
         <f>C4/B4</f>
-        <v>0</v>
+        <v>0.5431034482758621</v>
       </c>
       <c r="J4" s="72">
         <f>D4/B4</f>
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="K4" s="68">
         <f>B4-C4</f>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="71" t="s">
+        <v>341</v>
+      </c>
+      <c r="B5" s="68">
         <v>10524</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="71"/>
-      <c r="B5" s="68"/>
-      <c r="C5" s="69"/>
+      <c r="C5" s="69">
+        <v>6314</v>
+      </c>
       <c r="D5" s="68"/>
       <c r="E5" s="68"/>
       <c r="F5" s="68"/>
@@ -5587,8 +5605,12 @@
       <c r="K5" s="68"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="71"/>
-      <c r="B6" s="68"/>
+      <c r="A6" s="71" t="s">
+        <v>342</v>
+      </c>
+      <c r="B6" s="68">
+        <v>5525</v>
+      </c>
       <c r="C6" s="69"/>
       <c r="D6" s="68"/>
       <c r="E6" s="68"/>
@@ -5599,8 +5621,12 @@
       <c r="K6" s="68"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="71"/>
-      <c r="B7" s="68"/>
+      <c r="A7" s="71" t="s">
+        <v>343</v>
+      </c>
+      <c r="B7" s="68">
+        <v>3445</v>
+      </c>
       <c r="C7" s="69"/>
       <c r="D7" s="68"/>
       <c r="E7" s="68"/>
@@ -5611,8 +5637,12 @@
       <c r="K7" s="68"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="71"/>
-      <c r="B8" s="68"/>
+      <c r="A8" s="71" t="s">
+        <v>344</v>
+      </c>
+      <c r="B8" s="68">
+        <v>8484</v>
+      </c>
       <c r="C8" s="69"/>
       <c r="D8" s="68"/>
       <c r="E8" s="68"/>
@@ -5643,28 +5673,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
@@ -5700,7 +5730,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="74"/>
-      <c r="G5" s="76">
+      <c r="G5" s="78">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5750,7 +5780,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="74"/>
-      <c r="G8" s="76">
+      <c r="G8" s="78">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -5984,6 +6014,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -5993,14 +6031,6 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6020,20 +6050,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6175,32 +6205,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10648,38 +10678,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B9AACA9-AE30-48FC-87D2-EE6E4C127361}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF51CF91-CEAA-4BD8-A0EC-49659F6B696C}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1513,13 +1513,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5594,15 +5594,39 @@
         <v>10524</v>
       </c>
       <c r="C5" s="69">
+        <v>0</v>
+      </c>
+      <c r="D5" s="69">
         <v>6314</v>
       </c>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="72"/>
-      <c r="K5" s="68"/>
+      <c r="E5" s="68">
+        <f>D5-C5</f>
+        <v>6314</v>
+      </c>
+      <c r="F5" s="68">
+        <f t="shared" ref="F5:F8" si="1">B5-D5</f>
+        <v>4210</v>
+      </c>
+      <c r="G5" s="68">
+        <f t="shared" ref="G5:G8" si="2">C5-E5</f>
+        <v>-6314</v>
+      </c>
+      <c r="H5" s="68">
+        <f>E5</f>
+        <v>6314</v>
+      </c>
+      <c r="I5" s="72">
+        <f>C5/B5</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="72">
+        <f>D5/B5</f>
+        <v>0.59996199163816044</v>
+      </c>
+      <c r="K5" s="68">
+        <f>B5-C5</f>
+        <v>10524</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="71" t="s">
@@ -5611,14 +5635,40 @@
       <c r="B6" s="68">
         <v>5525</v>
       </c>
-      <c r="C6" s="69"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="72"/>
-      <c r="K6" s="68"/>
+      <c r="C6" s="69">
+        <v>0</v>
+      </c>
+      <c r="D6" s="68">
+        <v>0</v>
+      </c>
+      <c r="E6" s="68">
+        <f>D6-C6</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="68">
+        <f t="shared" si="1"/>
+        <v>5525</v>
+      </c>
+      <c r="G6" s="68">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="68">
+        <f>E6</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="72">
+        <f>C6/B6</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="72">
+        <f>D6/B6</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="68">
+        <f>B6-C6</f>
+        <v>5525</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="71" t="s">
@@ -5627,14 +5677,40 @@
       <c r="B7" s="68">
         <v>3445</v>
       </c>
-      <c r="C7" s="69"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="72"/>
-      <c r="K7" s="68"/>
+      <c r="C7" s="69">
+        <v>0</v>
+      </c>
+      <c r="D7" s="68">
+        <v>0</v>
+      </c>
+      <c r="E7" s="68">
+        <f>D7-C7</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="68">
+        <f t="shared" si="1"/>
+        <v>3445</v>
+      </c>
+      <c r="G7" s="68">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="68">
+        <f>E7</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="72">
+        <f>C7/B7</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="72">
+        <f>D7/B7</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="68">
+        <f>B7-C7</f>
+        <v>3445</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="71" t="s">
@@ -5643,14 +5719,40 @@
       <c r="B8" s="68">
         <v>8484</v>
       </c>
-      <c r="C8" s="69"/>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="72"/>
-      <c r="K8" s="68"/>
+      <c r="C8" s="69">
+        <v>0</v>
+      </c>
+      <c r="D8" s="68">
+        <v>0</v>
+      </c>
+      <c r="E8" s="68">
+        <f>D8-C8</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="68">
+        <f t="shared" si="1"/>
+        <v>8484</v>
+      </c>
+      <c r="G8" s="68">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="68">
+        <f>E8</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="72">
+        <f>C8/B8</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="72">
+        <f>D8/B8</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="68">
+        <f>B8-C8</f>
+        <v>8484</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5673,28 +5775,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
@@ -5730,7 +5832,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="74"/>
-      <c r="G5" s="78">
+      <c r="G5" s="76">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5780,7 +5882,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="74"/>
-      <c r="G8" s="78">
+      <c r="G8" s="76">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -6014,14 +6116,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6031,6 +6125,14 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6050,20 +6152,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6205,32 +6307,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10678,38 +10780,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF51CF91-CEAA-4BD8-A0EC-49659F6B696C}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D894AA-57A1-4FCF-AFD1-0BFC6F9D80B5}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="346">
   <si>
     <t>PRESUPUESTO TOTAL</t>
   </si>
@@ -1063,6 +1063,9 @@
   </si>
   <si>
     <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>CONSOLIDADO OBRAS</t>
   </si>
 </sst>
 </file>
@@ -1320,7 +1323,7 @@
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1513,13 +1516,16 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5409,7 +5415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FB8E136-486C-4EB9-920D-6287CDC3043B}">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" style="32" bestFit="1" customWidth="1"/>
@@ -5474,31 +5480,31 @@
         <v>39324.74</v>
       </c>
       <c r="E2" s="68">
-        <f>D2-C2</f>
+        <f t="shared" ref="E2:E8" si="0">D2-C2</f>
         <v>16554.499999999996</v>
       </c>
       <c r="F2" s="68">
-        <f t="shared" ref="F2:G4" si="0">B2-D2</f>
+        <f t="shared" ref="F2:G4" si="1">B2-D2</f>
         <v>0</v>
       </c>
       <c r="G2" s="68">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6215.7400000000052</v>
       </c>
       <c r="H2" s="68">
-        <f>E2</f>
+        <f t="shared" ref="H2:H8" si="2">E2</f>
         <v>16554.499999999996</v>
       </c>
       <c r="I2" s="72">
-        <f>C2/B2</f>
+        <f t="shared" ref="I2:I8" si="3">C2/B2</f>
         <v>0.57903091031243947</v>
       </c>
       <c r="J2" s="72">
-        <f>D2/B2</f>
+        <f t="shared" ref="J2:J8" si="4">D2/B2</f>
         <v>1</v>
       </c>
       <c r="K2" s="68">
-        <f>B2-C2</f>
+        <f t="shared" ref="K2:K8" si="5">B2-C2</f>
         <v>16554.499999999996</v>
       </c>
     </row>
@@ -5516,31 +5522,31 @@
         <v>406</v>
       </c>
       <c r="E3" s="68">
-        <f>D3-C3</f>
+        <f t="shared" si="0"/>
         <v>91</v>
       </c>
       <c r="F3" s="68">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>174</v>
       </c>
       <c r="G3" s="68">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>224</v>
       </c>
       <c r="H3" s="68">
-        <f>E3</f>
+        <f t="shared" si="2"/>
         <v>91</v>
       </c>
       <c r="I3" s="72">
-        <f>C3/B3</f>
+        <f t="shared" si="3"/>
         <v>0.5431034482758621</v>
       </c>
       <c r="J3" s="72">
-        <f>D3/B3</f>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="K3" s="68">
-        <f>B3-C3</f>
+        <f t="shared" si="5"/>
         <v>265</v>
       </c>
     </row>
@@ -5558,31 +5564,31 @@
         <v>406</v>
       </c>
       <c r="E4" s="68">
-        <f>D4-C4</f>
+        <f t="shared" si="0"/>
         <v>91</v>
       </c>
       <c r="F4" s="68">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>174</v>
       </c>
       <c r="G4" s="68">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>224</v>
       </c>
       <c r="H4" s="68">
-        <f>E4</f>
+        <f t="shared" si="2"/>
         <v>91</v>
       </c>
       <c r="I4" s="72">
-        <f>C4/B4</f>
+        <f t="shared" si="3"/>
         <v>0.5431034482758621</v>
       </c>
       <c r="J4" s="72">
-        <f>D4/B4</f>
+        <f t="shared" si="4"/>
         <v>0.7</v>
       </c>
       <c r="K4" s="68">
-        <f>B4-C4</f>
+        <f t="shared" si="5"/>
         <v>265</v>
       </c>
     </row>
@@ -5600,31 +5606,31 @@
         <v>6314</v>
       </c>
       <c r="E5" s="68">
-        <f>D5-C5</f>
+        <f t="shared" si="0"/>
         <v>6314</v>
       </c>
       <c r="F5" s="68">
-        <f t="shared" ref="F5:F8" si="1">B5-D5</f>
+        <f t="shared" ref="F5:F8" si="6">B5-D5</f>
         <v>4210</v>
       </c>
       <c r="G5" s="68">
-        <f t="shared" ref="G5:G8" si="2">C5-E5</f>
+        <f t="shared" ref="G5:G8" si="7">C5-E5</f>
         <v>-6314</v>
       </c>
       <c r="H5" s="68">
-        <f>E5</f>
+        <f t="shared" si="2"/>
         <v>6314</v>
       </c>
       <c r="I5" s="72">
-        <f>C5/B5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J5" s="72">
-        <f>D5/B5</f>
+        <f t="shared" si="4"/>
         <v>0.59996199163816044</v>
       </c>
       <c r="K5" s="68">
-        <f>B5-C5</f>
+        <f t="shared" si="5"/>
         <v>10524</v>
       </c>
     </row>
@@ -5642,31 +5648,31 @@
         <v>0</v>
       </c>
       <c r="E6" s="68">
-        <f>D6-C6</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F6" s="68">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>5525</v>
       </c>
       <c r="G6" s="68">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="68">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H6" s="68">
-        <f>E6</f>
-        <v>0</v>
-      </c>
       <c r="I6" s="72">
-        <f>C6/B6</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J6" s="72">
-        <f>D6/B6</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K6" s="68">
-        <f>B6-C6</f>
+        <f t="shared" si="5"/>
         <v>5525</v>
       </c>
     </row>
@@ -5684,31 +5690,31 @@
         <v>0</v>
       </c>
       <c r="E7" s="68">
-        <f>D7-C7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F7" s="68">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3445</v>
       </c>
       <c r="G7" s="68">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="68">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H7" s="68">
-        <f>E7</f>
-        <v>0</v>
-      </c>
       <c r="I7" s="72">
-        <f>C7/B7</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J7" s="72">
-        <f>D7/B7</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K7" s="68">
-        <f>B7-C7</f>
+        <f t="shared" si="5"/>
         <v>3445</v>
       </c>
     </row>
@@ -5726,36 +5732,82 @@
         <v>0</v>
       </c>
       <c r="E8" s="68">
-        <f>D8-C8</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F8" s="68">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>8484</v>
       </c>
       <c r="G8" s="68">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="68">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H8" s="68">
-        <f>E8</f>
-        <v>0</v>
-      </c>
       <c r="I8" s="72">
-        <f>C8/B8</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J8" s="72">
-        <f>D8/B8</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K8" s="68">
-        <f>B8-C8</f>
+        <f t="shared" si="5"/>
         <v>8484</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="71" t="s">
+        <v>345</v>
+      </c>
+      <c r="B9" s="79">
+        <f>SUM(B2:B8)</f>
+        <v>68462.739999999991</v>
+      </c>
+      <c r="C9" s="79">
+        <f>SUM(C2:C8)</f>
+        <v>23400.240000000002</v>
+      </c>
+      <c r="D9" s="79">
+        <f>SUM(D2:D8)</f>
+        <v>46450.74</v>
+      </c>
+      <c r="E9" s="68">
+        <f t="shared" ref="E9" si="8">D9-C9</f>
+        <v>23050.499999999996</v>
+      </c>
+      <c r="F9" s="68">
+        <f t="shared" ref="F9" si="9">B9-D9</f>
+        <v>22011.999999999993</v>
+      </c>
+      <c r="G9" s="68">
+        <f t="shared" ref="G9" si="10">C9-E9</f>
+        <v>349.74000000000524</v>
+      </c>
+      <c r="H9" s="68">
+        <f t="shared" ref="H9" si="11">E9</f>
+        <v>23050.499999999996</v>
+      </c>
+      <c r="I9" s="72">
+        <f t="shared" ref="I9" si="12">C9/B9</f>
+        <v>0.34179525972813835</v>
+      </c>
+      <c r="J9" s="72">
+        <f t="shared" ref="J9" si="13">D9/B9</f>
+        <v>0.67848204731507977</v>
+      </c>
+      <c r="K9" s="68">
+        <f t="shared" ref="K9" si="14">B9-C9</f>
+        <v>45062.499999999985</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5775,28 +5827,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="73" t="s">
@@ -5832,7 +5884,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="74"/>
-      <c r="G5" s="76">
+      <c r="G5" s="78">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5882,7 +5934,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="74"/>
-      <c r="G8" s="76">
+      <c r="G8" s="78">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -6116,6 +6168,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6125,14 +6185,6 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6152,20 +6204,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6307,32 +6359,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10780,38 +10832,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="76" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
+      <c r="J1" s="77"/>
+      <c r="K1" s="77"/>
+      <c r="L1" s="77"/>
+      <c r="M1" s="77"/>
+      <c r="N1" s="77"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
+      <c r="A2" s="77"/>
+      <c r="B2" s="77"/>
+      <c r="C2" s="77"/>
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77"/>
+      <c r="G2" s="77"/>
+      <c r="H2" s="77"/>
+      <c r="I2" s="77"/>
+      <c r="J2" s="77"/>
+      <c r="K2" s="77"/>
+      <c r="L2" s="77"/>
+      <c r="M2" s="77"/>
+      <c r="N2" s="77"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D894AA-57A1-4FCF-AFD1-0BFC6F9D80B5}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53BDC7A4-A8FC-40E3-8E9C-F74DFDE30BD9}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1509,6 +1509,9 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1516,16 +1519,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5474,14 +5474,14 @@
         <v>39324.74</v>
       </c>
       <c r="C2" s="69">
-        <v>22770.240000000002</v>
+        <v>20776.57</v>
       </c>
       <c r="D2" s="68">
         <v>39324.74</v>
       </c>
       <c r="E2" s="68">
         <f t="shared" ref="E2:E8" si="0">D2-C2</f>
-        <v>16554.499999999996</v>
+        <v>18548.169999999998</v>
       </c>
       <c r="F2" s="68">
         <f t="shared" ref="F2:G4" si="1">B2-D2</f>
@@ -5489,15 +5489,15 @@
       </c>
       <c r="G2" s="68">
         <f t="shared" si="1"/>
-        <v>6215.7400000000052</v>
+        <v>2228.4000000000015</v>
       </c>
       <c r="H2" s="68">
         <f t="shared" ref="H2:H8" si="2">E2</f>
-        <v>16554.499999999996</v>
+        <v>18548.169999999998</v>
       </c>
       <c r="I2" s="72">
         <f t="shared" ref="I2:I8" si="3">C2/B2</f>
-        <v>0.57903091031243947</v>
+        <v>0.52833330875169171</v>
       </c>
       <c r="J2" s="72">
         <f t="shared" ref="J2:J8" si="4">D2/B2</f>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="K2" s="68">
         <f t="shared" ref="K2:K8" si="5">B2-C2</f>
-        <v>16554.499999999996</v>
+        <v>18548.169999999998</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -5764,21 +5764,21 @@
       <c r="A9" s="71" t="s">
         <v>345</v>
       </c>
-      <c r="B9" s="79">
+      <c r="B9" s="73">
         <f>SUM(B2:B8)</f>
         <v>68462.739999999991</v>
       </c>
-      <c r="C9" s="79">
+      <c r="C9" s="73">
         <f>SUM(C2:C8)</f>
-        <v>23400.240000000002</v>
-      </c>
-      <c r="D9" s="79">
+        <v>21406.57</v>
+      </c>
+      <c r="D9" s="73">
         <f>SUM(D2:D8)</f>
         <v>46450.74</v>
       </c>
       <c r="E9" s="68">
         <f t="shared" ref="E9" si="8">D9-C9</f>
-        <v>23050.499999999996</v>
+        <v>25044.17</v>
       </c>
       <c r="F9" s="68">
         <f t="shared" ref="F9" si="9">B9-D9</f>
@@ -5786,15 +5786,15 @@
       </c>
       <c r="G9" s="68">
         <f t="shared" ref="G9" si="10">C9-E9</f>
-        <v>349.74000000000524</v>
+        <v>-3637.5999999999985</v>
       </c>
       <c r="H9" s="68">
         <f t="shared" ref="H9" si="11">E9</f>
-        <v>23050.499999999996</v>
+        <v>25044.17</v>
       </c>
       <c r="I9" s="72">
         <f t="shared" ref="I9" si="12">C9/B9</f>
-        <v>0.34179525972813835</v>
+        <v>0.31267474833756292</v>
       </c>
       <c r="J9" s="72">
         <f t="shared" ref="J9" si="13">D9/B9</f>
@@ -5802,7 +5802,7 @@
       </c>
       <c r="K9" s="68">
         <f t="shared" ref="K9" si="14">B9-C9</f>
-        <v>45062.499999999985</v>
+        <v>47056.169999999991</v>
       </c>
     </row>
   </sheetData>
@@ -5827,128 +5827,128 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="74"/>
-      <c r="C4" s="73" t="s">
+      <c r="A4" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="75"/>
+      <c r="C4" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="74"/>
-      <c r="E4" s="73" t="s">
+      <c r="D4" s="75"/>
+      <c r="E4" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="74"/>
-      <c r="G4" s="73" t="s">
+      <c r="F4" s="75"/>
+      <c r="G4" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="H4" s="74"/>
+      <c r="H4" s="75"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="75">
+      <c r="A5" s="76">
         <f>Presupuesto!E11</f>
         <v>43821.59</v>
       </c>
-      <c r="B5" s="74"/>
-      <c r="C5" s="75">
+      <c r="B5" s="75"/>
+      <c r="C5" s="76">
         <f>Compras_Materiales!L120+Pago_Obreros!M47</f>
         <v>21784.026381865144</v>
       </c>
-      <c r="D5" s="74"/>
-      <c r="E5" s="75">
+      <c r="D5" s="75"/>
+      <c r="E5" s="76">
         <f>A5-C5</f>
         <v>22037.563618134853</v>
       </c>
-      <c r="F5" s="74"/>
-      <c r="G5" s="78">
+      <c r="F5" s="75"/>
+      <c r="G5" s="77">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
-      <c r="H5" s="74"/>
+      <c r="H5" s="75"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="74"/>
-      <c r="B6" s="74"/>
-      <c r="C6" s="74"/>
-      <c r="D6" s="74"/>
-      <c r="E6" s="74"/>
-      <c r="F6" s="74"/>
-      <c r="G6" s="74"/>
-      <c r="H6" s="74"/>
+      <c r="A6" s="75"/>
+      <c r="B6" s="75"/>
+      <c r="C6" s="75"/>
+      <c r="D6" s="75"/>
+      <c r="E6" s="75"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75"/>
+      <c r="H6" s="75"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="73" t="s">
+      <c r="A7" s="74" t="s">
         <v>153</v>
       </c>
-      <c r="B7" s="74"/>
-      <c r="C7" s="73" t="s">
+      <c r="B7" s="75"/>
+      <c r="C7" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="74"/>
-      <c r="E7" s="73" t="s">
+      <c r="D7" s="75"/>
+      <c r="E7" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="74"/>
-      <c r="G7" s="73" t="s">
+      <c r="F7" s="75"/>
+      <c r="G7" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="H7" s="74"/>
+      <c r="H7" s="75"/>
     </row>
     <row r="8" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="75">
+      <c r="A8" s="76">
         <f>B23</f>
         <v>33203.99</v>
       </c>
-      <c r="B8" s="74"/>
-      <c r="C8" s="75">
+      <c r="B8" s="75"/>
+      <c r="C8" s="76">
         <f>C14</f>
         <v>21784.026381865144</v>
       </c>
-      <c r="D8" s="74"/>
-      <c r="E8" s="75">
+      <c r="D8" s="75"/>
+      <c r="E8" s="76">
         <f>A8-C8</f>
         <v>11419.963618134854</v>
       </c>
-      <c r="F8" s="74"/>
-      <c r="G8" s="78">
+      <c r="F8" s="75"/>
+      <c r="G8" s="77">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
-      <c r="H8" s="74"/>
+      <c r="H8" s="75"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="74"/>
-      <c r="B9" s="74"/>
-      <c r="C9" s="74"/>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="74"/>
+      <c r="A9" s="75"/>
+      <c r="B9" s="75"/>
+      <c r="C9" s="75"/>
+      <c r="D9" s="75"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
+      <c r="G9" s="75"/>
+      <c r="H9" s="75"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -6168,14 +6168,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6185,6 +6177,14 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6204,20 +6204,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6359,32 +6359,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10832,38 +10832,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="78" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="77"/>
-      <c r="L1" s="77"/>
-      <c r="M1" s="77"/>
-      <c r="N1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="77"/>
-      <c r="B2" s="77"/>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="79"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53BDC7A4-A8FC-40E3-8E9C-F74DFDE30BD9}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C906D4-0F58-449C-B36F-83F75C83D40A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-5805" yWindow="1800" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen Financiero" sheetId="9" r:id="rId1"/>
@@ -1519,13 +1519,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5471,41 +5471,41 @@
         <v>338</v>
       </c>
       <c r="B2" s="68">
-        <v>39324.74</v>
+        <v>38605.82</v>
       </c>
       <c r="C2" s="69">
-        <v>20776.57</v>
+        <v>24077.24</v>
       </c>
       <c r="D2" s="68">
-        <v>39324.74</v>
+        <v>33775.15</v>
       </c>
       <c r="E2" s="68">
         <f t="shared" ref="E2:E8" si="0">D2-C2</f>
-        <v>18548.169999999998</v>
+        <v>9697.91</v>
       </c>
       <c r="F2" s="68">
         <f t="shared" ref="F2:G4" si="1">B2-D2</f>
-        <v>0</v>
+        <v>4830.6699999999983</v>
       </c>
       <c r="G2" s="68">
         <f t="shared" si="1"/>
-        <v>2228.4000000000015</v>
+        <v>14379.330000000002</v>
       </c>
       <c r="H2" s="68">
         <f t="shared" ref="H2:H8" si="2">E2</f>
-        <v>18548.169999999998</v>
+        <v>9697.91</v>
       </c>
       <c r="I2" s="72">
         <f t="shared" ref="I2:I8" si="3">C2/B2</f>
-        <v>0.52833330875169171</v>
+        <v>0.62366865928505089</v>
       </c>
       <c r="J2" s="72">
         <f t="shared" ref="J2:J8" si="4">D2/B2</f>
-        <v>1</v>
+        <v>0.87487197526176108</v>
       </c>
       <c r="K2" s="68">
         <f t="shared" ref="K2:K8" si="5">B2-C2</f>
-        <v>18548.169999999998</v>
+        <v>14528.579999999998</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -5766,43 +5766,43 @@
       </c>
       <c r="B9" s="73">
         <f>SUM(B2:B8)</f>
-        <v>68462.739999999991</v>
+        <v>67743.820000000007</v>
       </c>
       <c r="C9" s="73">
         <f>SUM(C2:C8)</f>
-        <v>21406.57</v>
+        <v>24707.24</v>
       </c>
       <c r="D9" s="73">
         <f>SUM(D2:D8)</f>
-        <v>46450.74</v>
+        <v>40901.15</v>
       </c>
       <c r="E9" s="68">
         <f t="shared" ref="E9" si="8">D9-C9</f>
-        <v>25044.17</v>
+        <v>16193.91</v>
       </c>
       <c r="F9" s="68">
         <f t="shared" ref="F9" si="9">B9-D9</f>
-        <v>22011.999999999993</v>
+        <v>26842.670000000006</v>
       </c>
       <c r="G9" s="68">
         <f t="shared" ref="G9" si="10">C9-E9</f>
-        <v>-3637.5999999999985</v>
+        <v>8513.3300000000017</v>
       </c>
       <c r="H9" s="68">
         <f t="shared" ref="H9" si="11">E9</f>
-        <v>25044.17</v>
+        <v>16193.91</v>
       </c>
       <c r="I9" s="72">
         <f t="shared" ref="I9" si="12">C9/B9</f>
-        <v>0.31267474833756292</v>
+        <v>0.36471577776393477</v>
       </c>
       <c r="J9" s="72">
         <f t="shared" ref="J9" si="13">D9/B9</f>
-        <v>0.67848204731507977</v>
+        <v>0.60376208486619143</v>
       </c>
       <c r="K9" s="68">
         <f t="shared" ref="K9" si="14">B9-C9</f>
-        <v>47056.169999999991</v>
+        <v>43036.58</v>
       </c>
     </row>
   </sheetData>
@@ -5827,28 +5827,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="74" t="s">
@@ -5884,7 +5884,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="75"/>
-      <c r="G5" s="77">
+      <c r="G5" s="79">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5934,7 +5934,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="75"/>
-      <c r="G8" s="77">
+      <c r="G8" s="79">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -6168,6 +6168,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6177,14 +6185,6 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6204,20 +6204,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6359,32 +6359,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10832,38 +10832,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79"/>
-      <c r="N2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,20 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C906D4-0F58-449C-B36F-83F75C83D40A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5243D580-9C8E-479F-B1D7-C2472AB9AB1F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5805" yWindow="1800" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen Financiero" sheetId="9" r:id="rId1"/>
-    <sheet name="Dashboard" sheetId="1" r:id="rId2"/>
-    <sheet name="Presupuesto" sheetId="2" r:id="rId3"/>
-    <sheet name="Compras_Materiales" sheetId="3" r:id="rId4"/>
-    <sheet name="Pago_Obreros" sheetId="4" r:id="rId5"/>
-    <sheet name="Pago nomina" sheetId="8" r:id="rId6"/>
-    <sheet name="Hoja1" sheetId="7" r:id="rId7"/>
-    <sheet name="Nomina" sheetId="5" r:id="rId8"/>
-    <sheet name="Calculos" sheetId="6" r:id="rId9"/>
+    <sheet name="Dashboard" sheetId="1" state="hidden" r:id="rId2"/>
+    <sheet name="Presupuesto" sheetId="2" state="hidden" r:id="rId3"/>
+    <sheet name="Compras_Materiales" sheetId="3" state="hidden" r:id="rId4"/>
+    <sheet name="Pago_Obreros" sheetId="4" state="hidden" r:id="rId5"/>
+    <sheet name="Pago nomina" sheetId="8" state="hidden" r:id="rId6"/>
+    <sheet name="Hoja1" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet name="Nomina" sheetId="5" state="hidden" r:id="rId8"/>
+    <sheet name="Calculos" sheetId="6" state="hidden" r:id="rId9"/>
   </sheets>
   <calcPr calcId="181029"/>
 </workbook>
@@ -1014,9 +1014,6 @@
     <t>Monto Contrato</t>
   </si>
   <si>
-    <t>Egresos Reales</t>
-  </si>
-  <si>
     <t>Por cobrar</t>
   </si>
   <si>
@@ -1032,12 +1029,6 @@
     <t>% Avance Cobrado</t>
   </si>
   <si>
-    <t>Cobrado Acumulado/Desembolsado</t>
-  </si>
-  <si>
-    <t>Estimado Acumulado/Ejecutado</t>
-  </si>
-  <si>
     <t>Saldo por Ejecutar</t>
   </si>
   <si>
@@ -1066,6 +1057,15 @@
   </si>
   <si>
     <t>CONSOLIDADO OBRAS</t>
+  </si>
+  <si>
+    <t>EJECUTADO</t>
+  </si>
+  <si>
+    <t>DESEMBOLSADO</t>
+  </si>
+  <si>
+    <t>FLUJO DE CAJA</t>
   </si>
 </sst>
 </file>
@@ -1519,13 +1519,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5418,14 +5418,14 @@
   <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" style="32" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.85546875" style="32" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" style="32" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.7109375" style="32" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="33.42578125" style="32" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14" style="32" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.42578125" style="32"/>
     <col min="7" max="7" width="13.140625" style="32" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" style="32" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" style="32" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="18.7109375" style="32" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.140625" style="72" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17" bestFit="1" customWidth="1"/>
@@ -5433,42 +5433,42 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B1" s="32" t="s">
         <v>327</v>
       </c>
       <c r="C1" s="32" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="D1" s="32" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="E1" s="32" t="s">
+        <v>345</v>
+      </c>
+      <c r="F1" s="32" t="s">
         <v>328</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="G1" s="32" t="s">
         <v>329</v>
       </c>
-      <c r="G1" s="32" t="s">
+      <c r="H1" s="32" t="s">
         <v>330</v>
       </c>
-      <c r="H1" s="32" t="s">
+      <c r="I1" s="32" t="s">
         <v>331</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="J1" s="72" t="s">
         <v>332</v>
       </c>
-      <c r="J1" s="72" t="s">
+      <c r="K1" s="32" t="s">
         <v>333</v>
-      </c>
-      <c r="K1" s="32" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="71" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B2" s="68">
         <v>38605.82</v>
@@ -5510,7 +5510,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="71" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B3" s="68">
         <v>580</v>
@@ -5552,7 +5552,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="71" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B4" s="68">
         <v>580</v>
@@ -5594,7 +5594,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="71" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B5" s="68">
         <v>10524</v>
@@ -5636,7 +5636,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="71" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B6" s="68">
         <v>5525</v>
@@ -5645,23 +5645,23 @@
         <v>0</v>
       </c>
       <c r="D6" s="68">
-        <v>0</v>
+        <v>5525</v>
       </c>
       <c r="E6" s="68">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5525</v>
       </c>
       <c r="F6" s="68">
         <f t="shared" si="6"/>
-        <v>5525</v>
+        <v>0</v>
       </c>
       <c r="G6" s="68">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-5525</v>
       </c>
       <c r="H6" s="68">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5525</v>
       </c>
       <c r="I6" s="72">
         <f t="shared" si="3"/>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="J6" s="72">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" s="68">
         <f t="shared" si="5"/>
@@ -5678,32 +5678,32 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="71" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B7" s="68">
-        <v>3445</v>
+        <v>1743.75</v>
       </c>
       <c r="C7" s="69">
         <v>0</v>
       </c>
       <c r="D7" s="68">
-        <v>0</v>
+        <v>1743</v>
       </c>
       <c r="E7" s="68">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1743</v>
       </c>
       <c r="F7" s="68">
         <f t="shared" si="6"/>
-        <v>3445</v>
+        <v>0.75</v>
       </c>
       <c r="G7" s="68">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-1743</v>
       </c>
       <c r="H7" s="68">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1743</v>
       </c>
       <c r="I7" s="72">
         <f t="shared" si="3"/>
@@ -5711,41 +5711,41 @@
       </c>
       <c r="J7" s="72">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.99956989247311823</v>
       </c>
       <c r="K7" s="68">
         <f t="shared" si="5"/>
-        <v>3445</v>
+        <v>1743.75</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="71" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B8" s="68">
-        <v>8484</v>
+        <v>8484.7900000000009</v>
       </c>
       <c r="C8" s="69">
         <v>0</v>
       </c>
       <c r="D8" s="68">
-        <v>0</v>
+        <v>5094</v>
       </c>
       <c r="E8" s="68">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5094</v>
       </c>
       <c r="F8" s="68">
         <f t="shared" si="6"/>
-        <v>8484</v>
+        <v>3390.7900000000009</v>
       </c>
       <c r="G8" s="68">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>-5094</v>
       </c>
       <c r="H8" s="68">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5094</v>
       </c>
       <c r="I8" s="72">
         <f t="shared" si="3"/>
@@ -5753,20 +5753,20 @@
       </c>
       <c r="J8" s="72">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.60036842396806511</v>
       </c>
       <c r="K8" s="68">
         <f t="shared" si="5"/>
-        <v>8484</v>
+        <v>8484.7900000000009</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="71" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B9" s="73">
         <f>SUM(B2:B8)</f>
-        <v>67743.820000000007</v>
+        <v>66043.360000000001</v>
       </c>
       <c r="C9" s="73">
         <f>SUM(C2:C8)</f>
@@ -5774,35 +5774,35 @@
       </c>
       <c r="D9" s="73">
         <f>SUM(D2:D8)</f>
-        <v>40901.15</v>
+        <v>53263.15</v>
       </c>
       <c r="E9" s="68">
         <f t="shared" ref="E9" si="8">D9-C9</f>
-        <v>16193.91</v>
+        <v>28555.91</v>
       </c>
       <c r="F9" s="68">
         <f t="shared" ref="F9" si="9">B9-D9</f>
-        <v>26842.670000000006</v>
+        <v>12780.21</v>
       </c>
       <c r="G9" s="68">
         <f t="shared" ref="G9" si="10">C9-E9</f>
-        <v>8513.3300000000017</v>
+        <v>-3848.6699999999983</v>
       </c>
       <c r="H9" s="68">
         <f t="shared" ref="H9" si="11">E9</f>
-        <v>16193.91</v>
+        <v>28555.91</v>
       </c>
       <c r="I9" s="72">
         <f t="shared" ref="I9" si="12">C9/B9</f>
-        <v>0.36471577776393477</v>
+        <v>0.37410634468022225</v>
       </c>
       <c r="J9" s="72">
         <f t="shared" ref="J9" si="13">D9/B9</f>
-        <v>0.60376208486619143</v>
+        <v>0.80648758633721851</v>
       </c>
       <c r="K9" s="68">
         <f t="shared" ref="K9" si="14">B9-C9</f>
-        <v>43036.58</v>
+        <v>41336.119999999995</v>
       </c>
     </row>
   </sheetData>
@@ -5827,28 +5827,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="74" t="s">
@@ -5884,7 +5884,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="75"/>
-      <c r="G5" s="79">
+      <c r="G5" s="77">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5934,7 +5934,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="75"/>
-      <c r="G8" s="79">
+      <c r="G8" s="77">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -6168,14 +6168,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6185,6 +6177,14 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6204,20 +6204,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6359,32 +6359,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10832,38 +10832,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="79"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5243D580-9C8E-479F-B1D7-C2472AB9AB1F}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10CB1E3-A90E-42CE-A900-F9A96EFD4C64}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1519,13 +1519,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5827,28 +5827,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="74" t="s">
@@ -5884,7 +5884,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="75"/>
-      <c r="G5" s="77">
+      <c r="G5" s="79">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5934,7 +5934,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="75"/>
-      <c r="G8" s="77">
+      <c r="G8" s="79">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -6168,6 +6168,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6177,14 +6185,6 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6204,20 +6204,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6359,32 +6359,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10832,38 +10832,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79"/>
-      <c r="N2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10CB1E3-A90E-42CE-A900-F9A96EFD4C64}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E6E33B-1F23-4348-BA42-C54EDE9EF798}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5687,23 +5687,23 @@
         <v>0</v>
       </c>
       <c r="D7" s="68">
-        <v>1743</v>
+        <v>1743.75</v>
       </c>
       <c r="E7" s="68">
         <f t="shared" si="0"/>
-        <v>1743</v>
+        <v>1743.75</v>
       </c>
       <c r="F7" s="68">
         <f t="shared" si="6"/>
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="G7" s="68">
         <f t="shared" si="7"/>
-        <v>-1743</v>
+        <v>-1743.75</v>
       </c>
       <c r="H7" s="68">
         <f t="shared" si="2"/>
-        <v>1743</v>
+        <v>1743.75</v>
       </c>
       <c r="I7" s="72">
         <f t="shared" si="3"/>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="J7" s="72">
         <f t="shared" si="4"/>
-        <v>0.99956989247311823</v>
+        <v>1</v>
       </c>
       <c r="K7" s="68">
         <f t="shared" si="5"/>
@@ -5774,23 +5774,23 @@
       </c>
       <c r="D9" s="73">
         <f>SUM(D2:D8)</f>
-        <v>53263.15</v>
+        <v>53263.9</v>
       </c>
       <c r="E9" s="68">
         <f t="shared" ref="E9" si="8">D9-C9</f>
-        <v>28555.91</v>
+        <v>28556.66</v>
       </c>
       <c r="F9" s="68">
         <f t="shared" ref="F9" si="9">B9-D9</f>
-        <v>12780.21</v>
+        <v>12779.46</v>
       </c>
       <c r="G9" s="68">
         <f t="shared" ref="G9" si="10">C9-E9</f>
-        <v>-3848.6699999999983</v>
+        <v>-3849.4199999999983</v>
       </c>
       <c r="H9" s="68">
         <f t="shared" ref="H9" si="11">E9</f>
-        <v>28555.91</v>
+        <v>28556.66</v>
       </c>
       <c r="I9" s="72">
         <f t="shared" ref="I9" si="12">C9/B9</f>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="J9" s="72">
         <f t="shared" ref="J9" si="13">D9/B9</f>
-        <v>0.80648758633721851</v>
+        <v>0.80649894251291876</v>
       </c>
       <c r="K9" s="68">
         <f t="shared" ref="K9" si="14">B9-C9</f>

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E6E33B-1F23-4348-BA42-C54EDE9EF798}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46463BBB-8C2D-432E-8C19-E4EA4274C605}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,10 @@
     <sheet name="Nomina" sheetId="5" state="hidden" r:id="rId8"/>
     <sheet name="Calculos" sheetId="6" state="hidden" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <externalReferences>
+    <externalReference r:id="rId10"/>
+  </externalReferences>
+  <calcPr calcId="181029" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -1519,13 +1522,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5069,6 +5072,25 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Panel_de_Control"/>
+      <sheetName val="Registro_Transacciones"/>
+      <sheetName val="Soporte de compras"/>
+      <sheetName val="Configuracion"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{13F6BECB-7179-4C82-ADFD-3F088CF2F13E}" name="Tabla6" displayName="Tabla6" ref="A4:E10" insertRowShift="1" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
   <autoFilter ref="A4:E10" xr:uid="{8ABC211C-7D80-490C-9B76-89253396DB9F}"/>
@@ -5471,17 +5493,20 @@
         <v>335</v>
       </c>
       <c r="B2" s="68">
+        <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>38605.82</v>
       </c>
       <c r="C2" s="69">
-        <v>24077.24</v>
+        <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
+        <v>24081.77</v>
       </c>
       <c r="D2" s="68">
+        <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>33775.15</v>
       </c>
       <c r="E2" s="68">
         <f t="shared" ref="E2:E8" si="0">D2-C2</f>
-        <v>9697.91</v>
+        <v>9693.380000000001</v>
       </c>
       <c r="F2" s="68">
         <f t="shared" ref="F2:G4" si="1">B2-D2</f>
@@ -5489,15 +5514,15 @@
       </c>
       <c r="G2" s="68">
         <f t="shared" si="1"/>
-        <v>14379.330000000002</v>
+        <v>14388.39</v>
       </c>
       <c r="H2" s="68">
         <f t="shared" ref="H2:H8" si="2">E2</f>
-        <v>9697.91</v>
+        <v>9693.380000000001</v>
       </c>
       <c r="I2" s="72">
         <f t="shared" ref="I2:I8" si="3">C2/B2</f>
-        <v>0.62366865928505089</v>
+        <v>0.62378599910583432</v>
       </c>
       <c r="J2" s="72">
         <f t="shared" ref="J2:J8" si="4">D2/B2</f>
@@ -5505,7 +5530,7 @@
       </c>
       <c r="K2" s="68">
         <f t="shared" ref="K2:K8" si="5">B2-C2</f>
-        <v>14528.579999999998</v>
+        <v>14524.05</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -5513,12 +5538,15 @@
         <v>336</v>
       </c>
       <c r="B3" s="68">
+        <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>580</v>
       </c>
       <c r="C3" s="69">
+        <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
         <v>315</v>
       </c>
       <c r="D3" s="68">
+        <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>406</v>
       </c>
       <c r="E3" s="68">
@@ -5555,12 +5583,15 @@
         <v>337</v>
       </c>
       <c r="B4" s="68">
+        <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>580</v>
       </c>
       <c r="C4" s="69">
+        <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
         <v>315</v>
       </c>
       <c r="D4" s="68">
+        <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>406</v>
       </c>
       <c r="E4" s="68">
@@ -5597,12 +5628,15 @@
         <v>338</v>
       </c>
       <c r="B5" s="68">
+        <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>10524</v>
       </c>
       <c r="C5" s="69">
+        <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
         <v>0</v>
       </c>
       <c r="D5" s="69">
+        <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>6314</v>
       </c>
       <c r="E5" s="68">
@@ -5639,12 +5673,15 @@
         <v>339</v>
       </c>
       <c r="B6" s="68">
+        <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>5525</v>
       </c>
       <c r="C6" s="69">
+        <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
         <v>0</v>
       </c>
       <c r="D6" s="68">
+        <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>5525</v>
       </c>
       <c r="E6" s="68">
@@ -5681,12 +5718,15 @@
         <v>340</v>
       </c>
       <c r="B7" s="68">
+        <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>1743.75</v>
       </c>
       <c r="C7" s="69">
+        <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
         <v>0</v>
       </c>
       <c r="D7" s="68">
+        <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>1743.75</v>
       </c>
       <c r="E7" s="68">
@@ -5723,12 +5763,15 @@
         <v>341</v>
       </c>
       <c r="B8" s="68">
+        <f>[1]!Panel_Control[[#This Row],[Monto del Contrato]]</f>
         <v>8484.7900000000009</v>
       </c>
       <c r="C8" s="69">
+        <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
         <v>0</v>
       </c>
       <c r="D8" s="68">
+        <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
         <v>5094</v>
       </c>
       <c r="E8" s="68">
@@ -5770,7 +5813,7 @@
       </c>
       <c r="C9" s="73">
         <f>SUM(C2:C8)</f>
-        <v>24707.24</v>
+        <v>24711.77</v>
       </c>
       <c r="D9" s="73">
         <f>SUM(D2:D8)</f>
@@ -5778,7 +5821,7 @@
       </c>
       <c r="E9" s="68">
         <f t="shared" ref="E9" si="8">D9-C9</f>
-        <v>28556.66</v>
+        <v>28552.13</v>
       </c>
       <c r="F9" s="68">
         <f t="shared" ref="F9" si="9">B9-D9</f>
@@ -5786,15 +5829,15 @@
       </c>
       <c r="G9" s="68">
         <f t="shared" ref="G9" si="10">C9-E9</f>
-        <v>-3849.4199999999983</v>
+        <v>-3840.3600000000006</v>
       </c>
       <c r="H9" s="68">
         <f t="shared" ref="H9" si="11">E9</f>
-        <v>28556.66</v>
+        <v>28552.13</v>
       </c>
       <c r="I9" s="72">
         <f t="shared" ref="I9" si="12">C9/B9</f>
-        <v>0.37410634468022225</v>
+        <v>0.37417493598145218</v>
       </c>
       <c r="J9" s="72">
         <f t="shared" ref="J9" si="13">D9/B9</f>
@@ -5802,7 +5845,7 @@
       </c>
       <c r="K9" s="68">
         <f t="shared" ref="K9" si="14">B9-C9</f>
-        <v>41336.119999999995</v>
+        <v>41331.589999999997</v>
       </c>
     </row>
   </sheetData>
@@ -5827,28 +5870,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="74" t="s">
@@ -5884,7 +5927,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="75"/>
-      <c r="G5" s="79">
+      <c r="G5" s="77">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5934,7 +5977,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="75"/>
-      <c r="G8" s="79">
+      <c r="G8" s="77">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -6168,14 +6211,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6185,6 +6220,14 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6204,20 +6247,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6359,32 +6402,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10832,38 +10875,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="79"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46463BBB-8C2D-432E-8C19-E4EA4274C605}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97DE3F41-492A-4C20-A167-E5967B63E9DA}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
   <externalReferences>
     <externalReference r:id="rId10"/>
   </externalReferences>
-  <calcPr calcId="181029" iterateDelta="1E-4"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -5498,7 +5498,7 @@
       </c>
       <c r="C2" s="69">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
-        <v>24081.77</v>
+        <v>24087.77</v>
       </c>
       <c r="D2" s="68">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="E2" s="68">
         <f t="shared" ref="E2:E8" si="0">D2-C2</f>
-        <v>9693.380000000001</v>
+        <v>9687.380000000001</v>
       </c>
       <c r="F2" s="68">
         <f t="shared" ref="F2:G4" si="1">B2-D2</f>
@@ -5514,15 +5514,15 @@
       </c>
       <c r="G2" s="68">
         <f t="shared" si="1"/>
-        <v>14388.39</v>
+        <v>14400.39</v>
       </c>
       <c r="H2" s="68">
         <f t="shared" ref="H2:H8" si="2">E2</f>
-        <v>9693.380000000001</v>
+        <v>9687.380000000001</v>
       </c>
       <c r="I2" s="72">
         <f t="shared" ref="I2:I8" si="3">C2/B2</f>
-        <v>0.62378599910583432</v>
+        <v>0.62394141608700449</v>
       </c>
       <c r="J2" s="72">
         <f t="shared" ref="J2:J8" si="4">D2/B2</f>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="K2" s="68">
         <f t="shared" ref="K2:K8" si="5">B2-C2</f>
-        <v>14524.05</v>
+        <v>14518.05</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="C9" s="73">
         <f>SUM(C2:C8)</f>
-        <v>24711.77</v>
+        <v>24717.77</v>
       </c>
       <c r="D9" s="73">
         <f>SUM(D2:D8)</f>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="E9" s="68">
         <f t="shared" ref="E9" si="8">D9-C9</f>
-        <v>28552.13</v>
+        <v>28546.13</v>
       </c>
       <c r="F9" s="68">
         <f t="shared" ref="F9" si="9">B9-D9</f>
@@ -5829,15 +5829,15 @@
       </c>
       <c r="G9" s="68">
         <f t="shared" ref="G9" si="10">C9-E9</f>
-        <v>-3840.3600000000006</v>
+        <v>-3828.3600000000006</v>
       </c>
       <c r="H9" s="68">
         <f t="shared" ref="H9" si="11">E9</f>
-        <v>28552.13</v>
+        <v>28546.13</v>
       </c>
       <c r="I9" s="72">
         <f t="shared" ref="I9" si="12">C9/B9</f>
-        <v>0.37417493598145218</v>
+        <v>0.37426578538705479</v>
       </c>
       <c r="J9" s="72">
         <f t="shared" ref="J9" si="13">D9/B9</f>
@@ -5845,7 +5845,7 @@
       </c>
       <c r="K9" s="68">
         <f t="shared" ref="K9" si="14">B9-C9</f>
-        <v>41331.589999999997</v>
+        <v>41325.589999999997</v>
       </c>
     </row>
   </sheetData>

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97DE3F41-492A-4C20-A167-E5967B63E9DA}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE1B989-E67E-457E-AB2A-FB9CE2557369}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1522,13 +1522,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5498,7 +5498,7 @@
       </c>
       <c r="C2" s="69">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
-        <v>24087.77</v>
+        <v>25621.65</v>
       </c>
       <c r="D2" s="68">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="E2" s="68">
         <f t="shared" ref="E2:E8" si="0">D2-C2</f>
-        <v>9687.380000000001</v>
+        <v>8153.5</v>
       </c>
       <c r="F2" s="68">
         <f t="shared" ref="F2:G4" si="1">B2-D2</f>
@@ -5514,15 +5514,15 @@
       </c>
       <c r="G2" s="68">
         <f t="shared" si="1"/>
-        <v>14400.39</v>
+        <v>17468.150000000001</v>
       </c>
       <c r="H2" s="68">
         <f t="shared" ref="H2:H8" si="2">E2</f>
-        <v>9687.380000000001</v>
+        <v>8153.5</v>
       </c>
       <c r="I2" s="72">
         <f t="shared" ref="I2:I8" si="3">C2/B2</f>
-        <v>0.62394141608700449</v>
+        <v>0.66367324926656146</v>
       </c>
       <c r="J2" s="72">
         <f t="shared" ref="J2:J8" si="4">D2/B2</f>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="K2" s="68">
         <f t="shared" ref="K2:K8" si="5">B2-C2</f>
-        <v>14518.05</v>
+        <v>12984.169999999998</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="C5" s="69">
         <f>[1]!Panel_Control[[#This Row],[Total Ejecutado]]</f>
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="D5" s="69">
         <f>[1]!Panel_Control[[#This Row],[Total Ingresos]]</f>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="E5" s="68">
         <f t="shared" si="0"/>
-        <v>6314</v>
+        <v>3114</v>
       </c>
       <c r="F5" s="68">
         <f t="shared" ref="F5:F8" si="6">B5-D5</f>
@@ -5649,15 +5649,15 @@
       </c>
       <c r="G5" s="68">
         <f t="shared" ref="G5:G8" si="7">C5-E5</f>
-        <v>-6314</v>
+        <v>86</v>
       </c>
       <c r="H5" s="68">
         <f t="shared" si="2"/>
-        <v>6314</v>
+        <v>3114</v>
       </c>
       <c r="I5" s="72">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.30406689471683768</v>
       </c>
       <c r="J5" s="72">
         <f t="shared" si="4"/>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="K5" s="68">
         <f t="shared" si="5"/>
-        <v>10524</v>
+        <v>7324</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="C9" s="73">
         <f>SUM(C2:C8)</f>
-        <v>24717.77</v>
+        <v>29451.65</v>
       </c>
       <c r="D9" s="73">
         <f>SUM(D2:D8)</f>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="E9" s="68">
         <f t="shared" ref="E9" si="8">D9-C9</f>
-        <v>28546.13</v>
+        <v>23812.25</v>
       </c>
       <c r="F9" s="68">
         <f t="shared" ref="F9" si="9">B9-D9</f>
@@ -5829,15 +5829,15 @@
       </c>
       <c r="G9" s="68">
         <f t="shared" ref="G9" si="10">C9-E9</f>
-        <v>-3828.3600000000006</v>
+        <v>5639.4000000000015</v>
       </c>
       <c r="H9" s="68">
         <f t="shared" ref="H9" si="11">E9</f>
-        <v>28546.13</v>
+        <v>23812.25</v>
       </c>
       <c r="I9" s="72">
         <f t="shared" ref="I9" si="12">C9/B9</f>
-        <v>0.37426578538705479</v>
+        <v>0.44594414941941174</v>
       </c>
       <c r="J9" s="72">
         <f t="shared" ref="J9" si="13">D9/B9</f>
@@ -5845,7 +5845,7 @@
       </c>
       <c r="K9" s="68">
         <f t="shared" ref="K9" si="14">B9-C9</f>
-        <v>41325.589999999997</v>
+        <v>36591.71</v>
       </c>
     </row>
   </sheetData>
@@ -5870,28 +5870,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="74" t="s">
@@ -5927,7 +5927,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="75"/>
-      <c r="G5" s="77">
+      <c r="G5" s="79">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5977,7 +5977,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="75"/>
-      <c r="G8" s="77">
+      <c r="G8" s="79">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -6211,6 +6211,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6220,14 +6228,6 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6247,20 +6247,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6402,32 +6402,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10875,38 +10875,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
-      <c r="N1" s="79"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="79"/>
-      <c r="B2" s="79"/>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="79"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="79"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="79"/>
-      <c r="L2" s="79"/>
-      <c r="M2" s="79"/>
-      <c r="N2" s="79"/>
+      <c r="A2" s="78"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="78"/>
+      <c r="I2" s="78"/>
+      <c r="J2" s="78"/>
+      <c r="K2" s="78"/>
+      <c r="L2" s="78"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="78"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Datos/Gestion Proyecto Fatima.xlsx
+++ b/Datos/Gestion Proyecto Fatima.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP I5\Documents\Dashboard_Obras\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE1B989-E67E-457E-AB2A-FB9CE2557369}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{434582C6-B063-4A49-AD3C-3E1E14C5AA28}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1522,13 +1522,13 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
@@ -5870,28 +5870,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="74" t="s">
@@ -5927,7 +5927,7 @@
         <v>22037.563618134853</v>
       </c>
       <c r="F5" s="75"/>
-      <c r="G5" s="79">
+      <c r="G5" s="77">
         <f>C5/A5</f>
         <v>0.49710716525496096</v>
       </c>
@@ -5977,7 +5977,7 @@
         <v>11419.963618134854</v>
       </c>
       <c r="F8" s="75"/>
-      <c r="G8" s="79">
+      <c r="G8" s="77">
         <f>C8/A8</f>
         <v>0.65606652639833785</v>
       </c>
@@ -6211,14 +6211,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E8:F9"/>
-    <mergeCell ref="G8:H9"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="E4:F4"/>
@@ -6228,6 +6220,14 @@
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E8:F9"/>
+    <mergeCell ref="G8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
@@ -6247,20 +6247,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -6402,32 +6402,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -10875,38 +10875,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="78"/>
-      <c r="L1" s="78"/>
-      <c r="M1" s="78"/>
-      <c r="N1" s="78"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+      <c r="N1" s="79"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="78"/>
-      <c r="B2" s="78"/>
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="78"/>
-      <c r="J2" s="78"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="78"/>
-      <c r="M2" s="78"/>
-      <c r="N2" s="78"/>
+      <c r="A2" s="79"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
+      <c r="E2" s="79"/>
+      <c r="F2" s="79"/>
+      <c r="G2" s="79"/>
+      <c r="H2" s="79"/>
+      <c r="I2" s="79"/>
+      <c r="J2" s="79"/>
+      <c r="K2" s="79"/>
+      <c r="L2" s="79"/>
+      <c r="M2" s="79"/>
+      <c r="N2" s="79"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
